--- a/docs/Projekt-Tracker_2.xlsx
+++ b/docs/Projekt-Tracker_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dateien\Dev\Godot\Point_and_Click_Adventure\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\GodotProjekte\Point_and_Click_Adventure\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0193F138-5C60-49FE-893E-34CB9344BF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B1F295-F268-436A-B6E7-A8D294DF373C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="186">
   <si>
     <t>Projekt-Tracker · Software Engineering and Game Technical Direction</t>
   </si>
@@ -575,6 +575,33 @@
   </si>
   <si>
     <t>Einrichtung des Repositories</t>
+  </si>
+  <si>
+    <t>Game Designer</t>
+  </si>
+  <si>
+    <t>Ideen angelegt</t>
+  </si>
+  <si>
+    <t>Technical Director</t>
+  </si>
+  <si>
+    <t>Semester Plan und Vorgehen</t>
+  </si>
+  <si>
+    <t>Als Game Designer im falschen Projekt gearbeitet (Commit ignorieren)</t>
+  </si>
+  <si>
+    <t>Producer</t>
+  </si>
+  <si>
+    <t>Repo aufgeräumt</t>
+  </si>
+  <si>
+    <t>Godot PCA Tutorial</t>
+  </si>
+  <si>
+    <t>Dokumentstruktur aktualisiert</t>
   </si>
 </sst>
 </file>
@@ -672,7 +699,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -695,11 +722,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9CED8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9CED8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -775,6 +813,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2942,107 +2986,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:B22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:2" ht="20" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="27" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:2" ht="26" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="27" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:2" ht="26" x14ac:dyDescent="0.35">
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B16" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="27" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" ht="26" x14ac:dyDescent="0.35">
       <c r="B22" s="5" t="s">
         <v>17</v>
       </c>
@@ -3056,7 +3100,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:D42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -3064,17 +3108,17 @@
     <col min="4" max="4" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="21" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:4" ht="20" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B5" s="8" t="s">
         <v>20</v>
       </c>
@@ -3083,7 +3127,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" s="8" t="s">
         <v>22</v>
       </c>
@@ -3092,7 +3136,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" s="8" t="s">
         <v>23</v>
       </c>
@@ -3101,12 +3145,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B9" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" s="8" t="s">
         <v>26</v>
       </c>
@@ -3118,7 +3162,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="8" t="s">
         <v>28</v>
       </c>
@@ -3130,7 +3174,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B12" s="8" t="s">
         <v>30</v>
       </c>
@@ -3142,7 +3186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B13" s="8" t="s">
         <v>32</v>
       </c>
@@ -3154,12 +3198,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B15" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B16" s="8" t="s">
         <v>35</v>
       </c>
@@ -3169,7 +3213,7 @@
       </c>
       <c r="D16" s="7"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="8" t="s">
         <v>36</v>
       </c>
@@ -3179,7 +3223,7 @@
       </c>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="8" t="s">
         <v>37</v>
       </c>
@@ -3189,7 +3233,7 @@
       </c>
       <c r="D18" s="7"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="8" t="s">
         <v>38</v>
       </c>
@@ -3199,7 +3243,7 @@
       </c>
       <c r="D19" s="7"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="8" t="s">
         <v>39</v>
       </c>
@@ -3211,12 +3255,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B22" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="8" t="s">
         <v>42</v>
       </c>
@@ -3228,7 +3272,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="8" t="s">
         <v>44</v>
       </c>
@@ -3238,7 +3282,7 @@
       </c>
       <c r="D24" s="7"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="8" t="s">
         <v>45</v>
       </c>
@@ -3248,7 +3292,7 @@
       </c>
       <c r="D25" s="7"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="8" t="s">
         <v>46</v>
       </c>
@@ -3258,7 +3302,7 @@
       </c>
       <c r="D26" s="7"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="8" t="s">
         <v>47</v>
       </c>
@@ -3270,12 +3314,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B29" s="10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="8" t="s">
         <v>50</v>
       </c>
@@ -3287,7 +3331,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="8" t="s">
         <v>52</v>
       </c>
@@ -3299,24 +3343,24 @@
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B33" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="8" t="s">
         <v>55</v>
       </c>
       <c r="C34" s="11">
         <f>SUM(Zeitlog!B2:B501)</f>
-        <v>2.5</v>
+        <v>7.37</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="8" t="s">
         <v>57</v>
       </c>
@@ -3328,7 +3372,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="8" t="s">
         <v>59</v>
       </c>
@@ -3338,46 +3382,46 @@
       </c>
       <c r="D36" s="7"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C37" s="11">
         <f>SUMIF(Zeitlog!C2:C501,"Producer",Zeitlog!B2:B501)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D37" s="7" t="str">
         <f t="shared" ref="D37:D42" si="0">IFERROR(TEXT(C37/$C$34,"0%")&amp;" der Gesamtzeit","")</f>
-        <v>0% der Gesamtzeit</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+        <v>7% der Gesamtzeit</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="8" t="s">
         <v>61</v>
       </c>
       <c r="C38" s="11">
         <f>SUMIF(Zeitlog!C2:C501,"Game Designer",Zeitlog!B2:B501)</f>
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="D38" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0% der Gesamtzeit</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+        <v>5% der Gesamtzeit</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B39" s="8" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="11">
         <f>SUMIF(Zeitlog!C2:C501,"Technical Director",Zeitlog!B2:B501)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>0% der Gesamtzeit</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+        <v>14% der Gesamtzeit</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B40" s="8" t="s">
         <v>63</v>
       </c>
@@ -3390,7 +3434,7 @@
         <v>0% der Gesamtzeit</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B41" s="8" t="s">
         <v>64</v>
       </c>
@@ -3403,17 +3447,17 @@
         <v>0% der Gesamtzeit</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B42" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C42" s="11">
         <f>SUMIF(Zeitlog!C2:C501,"Einarbeitung / Lernen",Zeitlog!B2:B501)</f>
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="D42" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>100% der Gesamtzeit</v>
+        <v>75% der Gesamtzeit</v>
       </c>
     </row>
   </sheetData>
@@ -3435,7 +3479,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F501"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -3444,7 +3488,7 @@
     <col min="6" max="6" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>66</v>
       </c>
@@ -3461,9 +3505,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="17">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="B2" s="18">
         <v>2.5</v>
@@ -3475,2995 +3519,3043 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="17">
+        <v>46310</v>
+      </c>
+      <c r="B3" s="21">
+        <v>0.25</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="17">
+        <v>46310</v>
+      </c>
+      <c r="B4" s="21">
+        <v>1</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="17">
+        <v>46313</v>
+      </c>
+      <c r="B5" s="21">
+        <v>0.12</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="17">
+        <v>46320</v>
+      </c>
+      <c r="B6" s="37">
+        <v>3</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="17">
+        <v>46323</v>
+      </c>
+      <c r="B7" s="21">
+        <v>0.25</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="17">
+        <v>46324</v>
+      </c>
+      <c r="B8" s="21">
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="20"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="20"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="20"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="20"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="20"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="20"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="20"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
       <c r="D15" s="22"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="20"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="20"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="20"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
       <c r="D18" s="22"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="20"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
       <c r="D19" s="22"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="20"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="20"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="20"/>
       <c r="B22" s="21"/>
       <c r="C22" s="22"/>
       <c r="D22" s="22"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="20"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
       <c r="D23" s="22"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="20"/>
       <c r="B24" s="21"/>
       <c r="C24" s="22"/>
       <c r="D24" s="22"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="20"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
       <c r="D25" s="22"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="20"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
       <c r="D26" s="22"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="20"/>
       <c r="B27" s="21"/>
       <c r="C27" s="22"/>
       <c r="D27" s="22"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="20"/>
       <c r="B28" s="21"/>
       <c r="C28" s="22"/>
       <c r="D28" s="22"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="20"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="20"/>
       <c r="B30" s="21"/>
       <c r="C30" s="22"/>
       <c r="D30" s="22"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="20"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
       <c r="D31" s="22"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="20"/>
       <c r="B32" s="21"/>
       <c r="C32" s="22"/>
       <c r="D32" s="22"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="20"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
       <c r="D33" s="22"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="20"/>
       <c r="B34" s="21"/>
       <c r="C34" s="22"/>
       <c r="D34" s="22"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="20"/>
       <c r="B35" s="21"/>
       <c r="C35" s="22"/>
       <c r="D35" s="22"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="20"/>
       <c r="B36" s="21"/>
       <c r="C36" s="22"/>
       <c r="D36" s="22"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="20"/>
       <c r="B37" s="21"/>
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="20"/>
       <c r="B38" s="21"/>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="20"/>
       <c r="B39" s="21"/>
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="20"/>
       <c r="B40" s="21"/>
       <c r="C40" s="22"/>
       <c r="D40" s="22"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="20"/>
       <c r="B41" s="21"/>
       <c r="C41" s="22"/>
       <c r="D41" s="22"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="20"/>
       <c r="B42" s="21"/>
       <c r="C42" s="22"/>
       <c r="D42" s="22"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="20"/>
       <c r="B43" s="21"/>
       <c r="C43" s="22"/>
       <c r="D43" s="22"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="20"/>
       <c r="B44" s="21"/>
       <c r="C44" s="22"/>
       <c r="D44" s="22"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="20"/>
       <c r="B45" s="21"/>
       <c r="C45" s="22"/>
       <c r="D45" s="22"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="20"/>
       <c r="B46" s="21"/>
       <c r="C46" s="22"/>
       <c r="D46" s="22"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="20"/>
       <c r="B47" s="21"/>
       <c r="C47" s="22"/>
       <c r="D47" s="22"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="20"/>
       <c r="B48" s="21"/>
       <c r="C48" s="22"/>
       <c r="D48" s="22"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="20"/>
       <c r="B49" s="21"/>
       <c r="C49" s="22"/>
       <c r="D49" s="22"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="20"/>
       <c r="B50" s="21"/>
       <c r="C50" s="22"/>
       <c r="D50" s="22"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="20"/>
       <c r="B51" s="21"/>
       <c r="C51" s="22"/>
       <c r="D51" s="22"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="20"/>
       <c r="B52" s="21"/>
       <c r="C52" s="22"/>
       <c r="D52" s="22"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="20"/>
       <c r="B53" s="21"/>
       <c r="C53" s="22"/>
       <c r="D53" s="22"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="20"/>
       <c r="B54" s="21"/>
       <c r="C54" s="22"/>
       <c r="D54" s="22"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="20"/>
       <c r="B55" s="21"/>
       <c r="C55" s="22"/>
       <c r="D55" s="22"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="20"/>
       <c r="B56" s="21"/>
       <c r="C56" s="22"/>
       <c r="D56" s="22"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="20"/>
       <c r="B57" s="21"/>
       <c r="C57" s="22"/>
       <c r="D57" s="22"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="20"/>
       <c r="B58" s="21"/>
       <c r="C58" s="22"/>
       <c r="D58" s="22"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="20"/>
       <c r="B59" s="21"/>
       <c r="C59" s="22"/>
       <c r="D59" s="22"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="20"/>
       <c r="B60" s="21"/>
       <c r="C60" s="22"/>
       <c r="D60" s="22"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="20"/>
       <c r="B61" s="21"/>
       <c r="C61" s="22"/>
       <c r="D61" s="22"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="20"/>
       <c r="B62" s="21"/>
       <c r="C62" s="22"/>
       <c r="D62" s="22"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="20"/>
       <c r="B63" s="21"/>
       <c r="C63" s="22"/>
       <c r="D63" s="22"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="20"/>
       <c r="B64" s="21"/>
       <c r="C64" s="22"/>
       <c r="D64" s="22"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="20"/>
       <c r="B65" s="21"/>
       <c r="C65" s="22"/>
       <c r="D65" s="22"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="20"/>
       <c r="B66" s="21"/>
       <c r="C66" s="22"/>
       <c r="D66" s="22"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="20"/>
       <c r="B67" s="21"/>
       <c r="C67" s="22"/>
       <c r="D67" s="22"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="20"/>
       <c r="B68" s="21"/>
       <c r="C68" s="22"/>
       <c r="D68" s="22"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="20"/>
       <c r="B69" s="21"/>
       <c r="C69" s="22"/>
       <c r="D69" s="22"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="20"/>
       <c r="B70" s="21"/>
       <c r="C70" s="22"/>
       <c r="D70" s="22"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="20"/>
       <c r="B71" s="21"/>
       <c r="C71" s="22"/>
       <c r="D71" s="22"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="20"/>
       <c r="B72" s="21"/>
       <c r="C72" s="22"/>
       <c r="D72" s="22"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="20"/>
       <c r="B73" s="21"/>
       <c r="C73" s="22"/>
       <c r="D73" s="22"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="20"/>
       <c r="B74" s="21"/>
       <c r="C74" s="22"/>
       <c r="D74" s="22"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="20"/>
       <c r="B75" s="21"/>
       <c r="C75" s="22"/>
       <c r="D75" s="22"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="20"/>
       <c r="B76" s="21"/>
       <c r="C76" s="22"/>
       <c r="D76" s="22"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="20"/>
       <c r="B77" s="21"/>
       <c r="C77" s="22"/>
       <c r="D77" s="22"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="20"/>
       <c r="B78" s="21"/>
       <c r="C78" s="22"/>
       <c r="D78" s="22"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="20"/>
       <c r="B79" s="21"/>
       <c r="C79" s="22"/>
       <c r="D79" s="22"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="20"/>
       <c r="B80" s="21"/>
       <c r="C80" s="22"/>
       <c r="D80" s="22"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="20"/>
       <c r="B81" s="21"/>
       <c r="C81" s="22"/>
       <c r="D81" s="22"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="20"/>
       <c r="B82" s="21"/>
       <c r="C82" s="22"/>
       <c r="D82" s="22"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="20"/>
       <c r="B83" s="21"/>
       <c r="C83" s="22"/>
       <c r="D83" s="22"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="20"/>
       <c r="B84" s="21"/>
       <c r="C84" s="22"/>
       <c r="D84" s="22"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="20"/>
       <c r="B85" s="21"/>
       <c r="C85" s="22"/>
       <c r="D85" s="22"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="20"/>
       <c r="B86" s="21"/>
       <c r="C86" s="22"/>
       <c r="D86" s="22"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="20"/>
       <c r="B87" s="21"/>
       <c r="C87" s="22"/>
       <c r="D87" s="22"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="20"/>
       <c r="B88" s="21"/>
       <c r="C88" s="22"/>
       <c r="D88" s="22"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="20"/>
       <c r="B89" s="21"/>
       <c r="C89" s="22"/>
       <c r="D89" s="22"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="20"/>
       <c r="B90" s="21"/>
       <c r="C90" s="22"/>
       <c r="D90" s="22"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="20"/>
       <c r="B91" s="21"/>
       <c r="C91" s="22"/>
       <c r="D91" s="22"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="20"/>
       <c r="B92" s="21"/>
       <c r="C92" s="22"/>
       <c r="D92" s="22"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="20"/>
       <c r="B93" s="21"/>
       <c r="C93" s="22"/>
       <c r="D93" s="22"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="20"/>
       <c r="B94" s="21"/>
       <c r="C94" s="22"/>
       <c r="D94" s="22"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="20"/>
       <c r="B95" s="21"/>
       <c r="C95" s="22"/>
       <c r="D95" s="22"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="20"/>
       <c r="B96" s="21"/>
       <c r="C96" s="22"/>
       <c r="D96" s="22"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="20"/>
       <c r="B97" s="21"/>
       <c r="C97" s="22"/>
       <c r="D97" s="22"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" s="20"/>
       <c r="B98" s="21"/>
       <c r="C98" s="22"/>
       <c r="D98" s="22"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" s="20"/>
       <c r="B99" s="21"/>
       <c r="C99" s="22"/>
       <c r="D99" s="22"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" s="20"/>
       <c r="B100" s="21"/>
       <c r="C100" s="22"/>
       <c r="D100" s="22"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="20"/>
       <c r="B101" s="21"/>
       <c r="C101" s="22"/>
       <c r="D101" s="22"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" s="20"/>
       <c r="B102" s="21"/>
       <c r="C102" s="22"/>
       <c r="D102" s="22"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" s="20"/>
       <c r="B103" s="21"/>
       <c r="C103" s="22"/>
       <c r="D103" s="22"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="20"/>
       <c r="B104" s="21"/>
       <c r="C104" s="22"/>
       <c r="D104" s="22"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" s="20"/>
       <c r="B105" s="21"/>
       <c r="C105" s="22"/>
       <c r="D105" s="22"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" s="20"/>
       <c r="B106" s="21"/>
       <c r="C106" s="22"/>
       <c r="D106" s="22"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" s="20"/>
       <c r="B107" s="21"/>
       <c r="C107" s="22"/>
       <c r="D107" s="22"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" s="20"/>
       <c r="B108" s="21"/>
       <c r="C108" s="22"/>
       <c r="D108" s="22"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" s="20"/>
       <c r="B109" s="21"/>
       <c r="C109" s="22"/>
       <c r="D109" s="22"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="20"/>
       <c r="B110" s="21"/>
       <c r="C110" s="22"/>
       <c r="D110" s="22"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="20"/>
       <c r="B111" s="21"/>
       <c r="C111" s="22"/>
       <c r="D111" s="22"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" s="20"/>
       <c r="B112" s="21"/>
       <c r="C112" s="22"/>
       <c r="D112" s="22"/>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="20"/>
       <c r="B113" s="21"/>
       <c r="C113" s="22"/>
       <c r="D113" s="22"/>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="20"/>
       <c r="B114" s="21"/>
       <c r="C114" s="22"/>
       <c r="D114" s="22"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="20"/>
       <c r="B115" s="21"/>
       <c r="C115" s="22"/>
       <c r="D115" s="22"/>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" s="20"/>
       <c r="B116" s="21"/>
       <c r="C116" s="22"/>
       <c r="D116" s="22"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" s="20"/>
       <c r="B117" s="21"/>
       <c r="C117" s="22"/>
       <c r="D117" s="22"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" s="20"/>
       <c r="B118" s="21"/>
       <c r="C118" s="22"/>
       <c r="D118" s="22"/>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" s="20"/>
       <c r="B119" s="21"/>
       <c r="C119" s="22"/>
       <c r="D119" s="22"/>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" s="20"/>
       <c r="B120" s="21"/>
       <c r="C120" s="22"/>
       <c r="D120" s="22"/>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" s="20"/>
       <c r="B121" s="21"/>
       <c r="C121" s="22"/>
       <c r="D121" s="22"/>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" s="20"/>
       <c r="B122" s="21"/>
       <c r="C122" s="22"/>
       <c r="D122" s="22"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="20"/>
       <c r="B123" s="21"/>
       <c r="C123" s="22"/>
       <c r="D123" s="22"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" s="20"/>
       <c r="B124" s="21"/>
       <c r="C124" s="22"/>
       <c r="D124" s="22"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" s="20"/>
       <c r="B125" s="21"/>
       <c r="C125" s="22"/>
       <c r="D125" s="22"/>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" s="20"/>
       <c r="B126" s="21"/>
       <c r="C126" s="22"/>
       <c r="D126" s="22"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" s="20"/>
       <c r="B127" s="21"/>
       <c r="C127" s="22"/>
       <c r="D127" s="22"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" s="20"/>
       <c r="B128" s="21"/>
       <c r="C128" s="22"/>
       <c r="D128" s="22"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" s="20"/>
       <c r="B129" s="21"/>
       <c r="C129" s="22"/>
       <c r="D129" s="22"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" s="20"/>
       <c r="B130" s="21"/>
       <c r="C130" s="22"/>
       <c r="D130" s="22"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" s="20"/>
       <c r="B131" s="21"/>
       <c r="C131" s="22"/>
       <c r="D131" s="22"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" s="20"/>
       <c r="B132" s="21"/>
       <c r="C132" s="22"/>
       <c r="D132" s="22"/>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" s="20"/>
       <c r="B133" s="21"/>
       <c r="C133" s="22"/>
       <c r="D133" s="22"/>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="20"/>
       <c r="B134" s="21"/>
       <c r="C134" s="22"/>
       <c r="D134" s="22"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" s="20"/>
       <c r="B135" s="21"/>
       <c r="C135" s="22"/>
       <c r="D135" s="22"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" s="20"/>
       <c r="B136" s="21"/>
       <c r="C136" s="22"/>
       <c r="D136" s="22"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" s="20"/>
       <c r="B137" s="21"/>
       <c r="C137" s="22"/>
       <c r="D137" s="22"/>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" s="20"/>
       <c r="B138" s="21"/>
       <c r="C138" s="22"/>
       <c r="D138" s="22"/>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" s="20"/>
       <c r="B139" s="21"/>
       <c r="C139" s="22"/>
       <c r="D139" s="22"/>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" s="20"/>
       <c r="B140" s="21"/>
       <c r="C140" s="22"/>
       <c r="D140" s="22"/>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" s="20"/>
       <c r="B141" s="21"/>
       <c r="C141" s="22"/>
       <c r="D141" s="22"/>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" s="20"/>
       <c r="B142" s="21"/>
       <c r="C142" s="22"/>
       <c r="D142" s="22"/>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" s="20"/>
       <c r="B143" s="21"/>
       <c r="C143" s="22"/>
       <c r="D143" s="22"/>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" s="20"/>
       <c r="B144" s="21"/>
       <c r="C144" s="22"/>
       <c r="D144" s="22"/>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" s="20"/>
       <c r="B145" s="21"/>
       <c r="C145" s="22"/>
       <c r="D145" s="22"/>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" s="20"/>
       <c r="B146" s="21"/>
       <c r="C146" s="22"/>
       <c r="D146" s="22"/>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" s="20"/>
       <c r="B147" s="21"/>
       <c r="C147" s="22"/>
       <c r="D147" s="22"/>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" s="20"/>
       <c r="B148" s="21"/>
       <c r="C148" s="22"/>
       <c r="D148" s="22"/>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" s="20"/>
       <c r="B149" s="21"/>
       <c r="C149" s="22"/>
       <c r="D149" s="22"/>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" s="20"/>
       <c r="B150" s="21"/>
       <c r="C150" s="22"/>
       <c r="D150" s="22"/>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" s="20"/>
       <c r="B151" s="21"/>
       <c r="C151" s="22"/>
       <c r="D151" s="22"/>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="20"/>
       <c r="B152" s="21"/>
       <c r="C152" s="22"/>
       <c r="D152" s="22"/>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="20"/>
       <c r="B153" s="21"/>
       <c r="C153" s="22"/>
       <c r="D153" s="22"/>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" s="20"/>
       <c r="B154" s="21"/>
       <c r="C154" s="22"/>
       <c r="D154" s="22"/>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" s="20"/>
       <c r="B155" s="21"/>
       <c r="C155" s="22"/>
       <c r="D155" s="22"/>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" s="20"/>
       <c r="B156" s="21"/>
       <c r="C156" s="22"/>
       <c r="D156" s="22"/>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" s="20"/>
       <c r="B157" s="21"/>
       <c r="C157" s="22"/>
       <c r="D157" s="22"/>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" s="20"/>
       <c r="B158" s="21"/>
       <c r="C158" s="22"/>
       <c r="D158" s="22"/>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" s="20"/>
       <c r="B159" s="21"/>
       <c r="C159" s="22"/>
       <c r="D159" s="22"/>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" s="20"/>
       <c r="B160" s="21"/>
       <c r="C160" s="22"/>
       <c r="D160" s="22"/>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" s="20"/>
       <c r="B161" s="21"/>
       <c r="C161" s="22"/>
       <c r="D161" s="22"/>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" s="20"/>
       <c r="B162" s="21"/>
       <c r="C162" s="22"/>
       <c r="D162" s="22"/>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" s="20"/>
       <c r="B163" s="21"/>
       <c r="C163" s="22"/>
       <c r="D163" s="22"/>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" s="20"/>
       <c r="B164" s="21"/>
       <c r="C164" s="22"/>
       <c r="D164" s="22"/>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" s="20"/>
       <c r="B165" s="21"/>
       <c r="C165" s="22"/>
       <c r="D165" s="22"/>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" s="20"/>
       <c r="B166" s="21"/>
       <c r="C166" s="22"/>
       <c r="D166" s="22"/>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" s="20"/>
       <c r="B167" s="21"/>
       <c r="C167" s="22"/>
       <c r="D167" s="22"/>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" s="20"/>
       <c r="B168" s="21"/>
       <c r="C168" s="22"/>
       <c r="D168" s="22"/>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" s="20"/>
       <c r="B169" s="21"/>
       <c r="C169" s="22"/>
       <c r="D169" s="22"/>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" s="20"/>
       <c r="B170" s="21"/>
       <c r="C170" s="22"/>
       <c r="D170" s="22"/>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" s="20"/>
       <c r="B171" s="21"/>
       <c r="C171" s="22"/>
       <c r="D171" s="22"/>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" s="20"/>
       <c r="B172" s="21"/>
       <c r="C172" s="22"/>
       <c r="D172" s="22"/>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" s="20"/>
       <c r="B173" s="21"/>
       <c r="C173" s="22"/>
       <c r="D173" s="22"/>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" s="20"/>
       <c r="B174" s="21"/>
       <c r="C174" s="22"/>
       <c r="D174" s="22"/>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" s="20"/>
       <c r="B175" s="21"/>
       <c r="C175" s="22"/>
       <c r="D175" s="22"/>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" s="20"/>
       <c r="B176" s="21"/>
       <c r="C176" s="22"/>
       <c r="D176" s="22"/>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" s="20"/>
       <c r="B177" s="21"/>
       <c r="C177" s="22"/>
       <c r="D177" s="22"/>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" s="20"/>
       <c r="B178" s="21"/>
       <c r="C178" s="22"/>
       <c r="D178" s="22"/>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" s="20"/>
       <c r="B179" s="21"/>
       <c r="C179" s="22"/>
       <c r="D179" s="22"/>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" s="20"/>
       <c r="B180" s="21"/>
       <c r="C180" s="22"/>
       <c r="D180" s="22"/>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" s="20"/>
       <c r="B181" s="21"/>
       <c r="C181" s="22"/>
       <c r="D181" s="22"/>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" s="20"/>
       <c r="B182" s="21"/>
       <c r="C182" s="22"/>
       <c r="D182" s="22"/>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" s="20"/>
       <c r="B183" s="21"/>
       <c r="C183" s="22"/>
       <c r="D183" s="22"/>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" s="20"/>
       <c r="B184" s="21"/>
       <c r="C184" s="22"/>
       <c r="D184" s="22"/>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" s="20"/>
       <c r="B185" s="21"/>
       <c r="C185" s="22"/>
       <c r="D185" s="22"/>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" s="20"/>
       <c r="B186" s="21"/>
       <c r="C186" s="22"/>
       <c r="D186" s="22"/>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" s="20"/>
       <c r="B187" s="21"/>
       <c r="C187" s="22"/>
       <c r="D187" s="22"/>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" s="20"/>
       <c r="B188" s="21"/>
       <c r="C188" s="22"/>
       <c r="D188" s="22"/>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" s="20"/>
       <c r="B189" s="21"/>
       <c r="C189" s="22"/>
       <c r="D189" s="22"/>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" s="20"/>
       <c r="B190" s="21"/>
       <c r="C190" s="22"/>
       <c r="D190" s="22"/>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" s="20"/>
       <c r="B191" s="21"/>
       <c r="C191" s="22"/>
       <c r="D191" s="22"/>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" s="20"/>
       <c r="B192" s="21"/>
       <c r="C192" s="22"/>
       <c r="D192" s="22"/>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" s="20"/>
       <c r="B193" s="21"/>
       <c r="C193" s="22"/>
       <c r="D193" s="22"/>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" s="20"/>
       <c r="B194" s="21"/>
       <c r="C194" s="22"/>
       <c r="D194" s="22"/>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" s="20"/>
       <c r="B195" s="21"/>
       <c r="C195" s="22"/>
       <c r="D195" s="22"/>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" s="20"/>
       <c r="B196" s="21"/>
       <c r="C196" s="22"/>
       <c r="D196" s="22"/>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" s="20"/>
       <c r="B197" s="21"/>
       <c r="C197" s="22"/>
       <c r="D197" s="22"/>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" s="20"/>
       <c r="B198" s="21"/>
       <c r="C198" s="22"/>
       <c r="D198" s="22"/>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" s="20"/>
       <c r="B199" s="21"/>
       <c r="C199" s="22"/>
       <c r="D199" s="22"/>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" s="20"/>
       <c r="B200" s="21"/>
       <c r="C200" s="22"/>
       <c r="D200" s="22"/>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" s="20"/>
       <c r="B201" s="21"/>
       <c r="C201" s="22"/>
       <c r="D201" s="22"/>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" s="20"/>
       <c r="B202" s="21"/>
       <c r="C202" s="22"/>
       <c r="D202" s="22"/>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" s="20"/>
       <c r="B203" s="21"/>
       <c r="C203" s="22"/>
       <c r="D203" s="22"/>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" s="20"/>
       <c r="B204" s="21"/>
       <c r="C204" s="22"/>
       <c r="D204" s="22"/>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" s="20"/>
       <c r="B205" s="21"/>
       <c r="C205" s="22"/>
       <c r="D205" s="22"/>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" s="20"/>
       <c r="B206" s="21"/>
       <c r="C206" s="22"/>
       <c r="D206" s="22"/>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" s="20"/>
       <c r="B207" s="21"/>
       <c r="C207" s="22"/>
       <c r="D207" s="22"/>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" s="20"/>
       <c r="B208" s="21"/>
       <c r="C208" s="22"/>
       <c r="D208" s="22"/>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" s="20"/>
       <c r="B209" s="21"/>
       <c r="C209" s="22"/>
       <c r="D209" s="22"/>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" s="20"/>
       <c r="B210" s="21"/>
       <c r="C210" s="22"/>
       <c r="D210" s="22"/>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" s="20"/>
       <c r="B211" s="21"/>
       <c r="C211" s="22"/>
       <c r="D211" s="22"/>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" s="20"/>
       <c r="B212" s="21"/>
       <c r="C212" s="22"/>
       <c r="D212" s="22"/>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" s="20"/>
       <c r="B213" s="21"/>
       <c r="C213" s="22"/>
       <c r="D213" s="22"/>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" s="20"/>
       <c r="B214" s="21"/>
       <c r="C214" s="22"/>
       <c r="D214" s="22"/>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" s="20"/>
       <c r="B215" s="21"/>
       <c r="C215" s="22"/>
       <c r="D215" s="22"/>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" s="20"/>
       <c r="B216" s="21"/>
       <c r="C216" s="22"/>
       <c r="D216" s="22"/>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" s="20"/>
       <c r="B217" s="21"/>
       <c r="C217" s="22"/>
       <c r="D217" s="22"/>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" s="20"/>
       <c r="B218" s="21"/>
       <c r="C218" s="22"/>
       <c r="D218" s="22"/>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" s="20"/>
       <c r="B219" s="21"/>
       <c r="C219" s="22"/>
       <c r="D219" s="22"/>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" s="20"/>
       <c r="B220" s="21"/>
       <c r="C220" s="22"/>
       <c r="D220" s="22"/>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" s="20"/>
       <c r="B221" s="21"/>
       <c r="C221" s="22"/>
       <c r="D221" s="22"/>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" s="20"/>
       <c r="B222" s="21"/>
       <c r="C222" s="22"/>
       <c r="D222" s="22"/>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" s="20"/>
       <c r="B223" s="21"/>
       <c r="C223" s="22"/>
       <c r="D223" s="22"/>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" s="20"/>
       <c r="B224" s="21"/>
       <c r="C224" s="22"/>
       <c r="D224" s="22"/>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" s="20"/>
       <c r="B225" s="21"/>
       <c r="C225" s="22"/>
       <c r="D225" s="22"/>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" s="20"/>
       <c r="B226" s="21"/>
       <c r="C226" s="22"/>
       <c r="D226" s="22"/>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" s="20"/>
       <c r="B227" s="21"/>
       <c r="C227" s="22"/>
       <c r="D227" s="22"/>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" s="20"/>
       <c r="B228" s="21"/>
       <c r="C228" s="22"/>
       <c r="D228" s="22"/>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" s="20"/>
       <c r="B229" s="21"/>
       <c r="C229" s="22"/>
       <c r="D229" s="22"/>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" s="20"/>
       <c r="B230" s="21"/>
       <c r="C230" s="22"/>
       <c r="D230" s="22"/>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" s="20"/>
       <c r="B231" s="21"/>
       <c r="C231" s="22"/>
       <c r="D231" s="22"/>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" s="20"/>
       <c r="B232" s="21"/>
       <c r="C232" s="22"/>
       <c r="D232" s="22"/>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" s="20"/>
       <c r="B233" s="21"/>
       <c r="C233" s="22"/>
       <c r="D233" s="22"/>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" s="20"/>
       <c r="B234" s="21"/>
       <c r="C234" s="22"/>
       <c r="D234" s="22"/>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A235" s="20"/>
       <c r="B235" s="21"/>
       <c r="C235" s="22"/>
       <c r="D235" s="22"/>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A236" s="20"/>
       <c r="B236" s="21"/>
       <c r="C236" s="22"/>
       <c r="D236" s="22"/>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A237" s="20"/>
       <c r="B237" s="21"/>
       <c r="C237" s="22"/>
       <c r="D237" s="22"/>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A238" s="20"/>
       <c r="B238" s="21"/>
       <c r="C238" s="22"/>
       <c r="D238" s="22"/>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A239" s="20"/>
       <c r="B239" s="21"/>
       <c r="C239" s="22"/>
       <c r="D239" s="22"/>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A240" s="20"/>
       <c r="B240" s="21"/>
       <c r="C240" s="22"/>
       <c r="D240" s="22"/>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" s="20"/>
       <c r="B241" s="21"/>
       <c r="C241" s="22"/>
       <c r="D241" s="22"/>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A242" s="20"/>
       <c r="B242" s="21"/>
       <c r="C242" s="22"/>
       <c r="D242" s="22"/>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A243" s="20"/>
       <c r="B243" s="21"/>
       <c r="C243" s="22"/>
       <c r="D243" s="22"/>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A244" s="20"/>
       <c r="B244" s="21"/>
       <c r="C244" s="22"/>
       <c r="D244" s="22"/>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A245" s="20"/>
       <c r="B245" s="21"/>
       <c r="C245" s="22"/>
       <c r="D245" s="22"/>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A246" s="20"/>
       <c r="B246" s="21"/>
       <c r="C246" s="22"/>
       <c r="D246" s="22"/>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A247" s="20"/>
       <c r="B247" s="21"/>
       <c r="C247" s="22"/>
       <c r="D247" s="22"/>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" s="20"/>
       <c r="B248" s="21"/>
       <c r="C248" s="22"/>
       <c r="D248" s="22"/>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" s="20"/>
       <c r="B249" s="21"/>
       <c r="C249" s="22"/>
       <c r="D249" s="22"/>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" s="20"/>
       <c r="B250" s="21"/>
       <c r="C250" s="22"/>
       <c r="D250" s="22"/>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" s="20"/>
       <c r="B251" s="21"/>
       <c r="C251" s="22"/>
       <c r="D251" s="22"/>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" s="20"/>
       <c r="B252" s="21"/>
       <c r="C252" s="22"/>
       <c r="D252" s="22"/>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" s="20"/>
       <c r="B253" s="21"/>
       <c r="C253" s="22"/>
       <c r="D253" s="22"/>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" s="20"/>
       <c r="B254" s="21"/>
       <c r="C254" s="22"/>
       <c r="D254" s="22"/>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" s="20"/>
       <c r="B255" s="21"/>
       <c r="C255" s="22"/>
       <c r="D255" s="22"/>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" s="20"/>
       <c r="B256" s="21"/>
       <c r="C256" s="22"/>
       <c r="D256" s="22"/>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" s="20"/>
       <c r="B257" s="21"/>
       <c r="C257" s="22"/>
       <c r="D257" s="22"/>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" s="20"/>
       <c r="B258" s="21"/>
       <c r="C258" s="22"/>
       <c r="D258" s="22"/>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" s="20"/>
       <c r="B259" s="21"/>
       <c r="C259" s="22"/>
       <c r="D259" s="22"/>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" s="20"/>
       <c r="B260" s="21"/>
       <c r="C260" s="22"/>
       <c r="D260" s="22"/>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" s="20"/>
       <c r="B261" s="21"/>
       <c r="C261" s="22"/>
       <c r="D261" s="22"/>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" s="20"/>
       <c r="B262" s="21"/>
       <c r="C262" s="22"/>
       <c r="D262" s="22"/>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" s="20"/>
       <c r="B263" s="21"/>
       <c r="C263" s="22"/>
       <c r="D263" s="22"/>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" s="20"/>
       <c r="B264" s="21"/>
       <c r="C264" s="22"/>
       <c r="D264" s="22"/>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" s="20"/>
       <c r="B265" s="21"/>
       <c r="C265" s="22"/>
       <c r="D265" s="22"/>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" s="20"/>
       <c r="B266" s="21"/>
       <c r="C266" s="22"/>
       <c r="D266" s="22"/>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" s="20"/>
       <c r="B267" s="21"/>
       <c r="C267" s="22"/>
       <c r="D267" s="22"/>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" s="20"/>
       <c r="B268" s="21"/>
       <c r="C268" s="22"/>
       <c r="D268" s="22"/>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" s="20"/>
       <c r="B269" s="21"/>
       <c r="C269" s="22"/>
       <c r="D269" s="22"/>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" s="20"/>
       <c r="B270" s="21"/>
       <c r="C270" s="22"/>
       <c r="D270" s="22"/>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" s="20"/>
       <c r="B271" s="21"/>
       <c r="C271" s="22"/>
       <c r="D271" s="22"/>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" s="20"/>
       <c r="B272" s="21"/>
       <c r="C272" s="22"/>
       <c r="D272" s="22"/>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" s="20"/>
       <c r="B273" s="21"/>
       <c r="C273" s="22"/>
       <c r="D273" s="22"/>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" s="20"/>
       <c r="B274" s="21"/>
       <c r="C274" s="22"/>
       <c r="D274" s="22"/>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" s="20"/>
       <c r="B275" s="21"/>
       <c r="C275" s="22"/>
       <c r="D275" s="22"/>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" s="20"/>
       <c r="B276" s="21"/>
       <c r="C276" s="22"/>
       <c r="D276" s="22"/>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" s="20"/>
       <c r="B277" s="21"/>
       <c r="C277" s="22"/>
       <c r="D277" s="22"/>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A278" s="20"/>
       <c r="B278" s="21"/>
       <c r="C278" s="22"/>
       <c r="D278" s="22"/>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A279" s="20"/>
       <c r="B279" s="21"/>
       <c r="C279" s="22"/>
       <c r="D279" s="22"/>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A280" s="20"/>
       <c r="B280" s="21"/>
       <c r="C280" s="22"/>
       <c r="D280" s="22"/>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A281" s="20"/>
       <c r="B281" s="21"/>
       <c r="C281" s="22"/>
       <c r="D281" s="22"/>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A282" s="20"/>
       <c r="B282" s="21"/>
       <c r="C282" s="22"/>
       <c r="D282" s="22"/>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A283" s="20"/>
       <c r="B283" s="21"/>
       <c r="C283" s="22"/>
       <c r="D283" s="22"/>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" s="20"/>
       <c r="B284" s="21"/>
       <c r="C284" s="22"/>
       <c r="D284" s="22"/>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A285" s="20"/>
       <c r="B285" s="21"/>
       <c r="C285" s="22"/>
       <c r="D285" s="22"/>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A286" s="20"/>
       <c r="B286" s="21"/>
       <c r="C286" s="22"/>
       <c r="D286" s="22"/>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" s="20"/>
       <c r="B287" s="21"/>
       <c r="C287" s="22"/>
       <c r="D287" s="22"/>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" s="20"/>
       <c r="B288" s="21"/>
       <c r="C288" s="22"/>
       <c r="D288" s="22"/>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" s="20"/>
       <c r="B289" s="21"/>
       <c r="C289" s="22"/>
       <c r="D289" s="22"/>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A290" s="20"/>
       <c r="B290" s="21"/>
       <c r="C290" s="22"/>
       <c r="D290" s="22"/>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A291" s="20"/>
       <c r="B291" s="21"/>
       <c r="C291" s="22"/>
       <c r="D291" s="22"/>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A292" s="20"/>
       <c r="B292" s="21"/>
       <c r="C292" s="22"/>
       <c r="D292" s="22"/>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A293" s="20"/>
       <c r="B293" s="21"/>
       <c r="C293" s="22"/>
       <c r="D293" s="22"/>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A294" s="20"/>
       <c r="B294" s="21"/>
       <c r="C294" s="22"/>
       <c r="D294" s="22"/>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A295" s="20"/>
       <c r="B295" s="21"/>
       <c r="C295" s="22"/>
       <c r="D295" s="22"/>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" s="20"/>
       <c r="B296" s="21"/>
       <c r="C296" s="22"/>
       <c r="D296" s="22"/>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" s="20"/>
       <c r="B297" s="21"/>
       <c r="C297" s="22"/>
       <c r="D297" s="22"/>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" s="20"/>
       <c r="B298" s="21"/>
       <c r="C298" s="22"/>
       <c r="D298" s="22"/>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" s="20"/>
       <c r="B299" s="21"/>
       <c r="C299" s="22"/>
       <c r="D299" s="22"/>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" s="20"/>
       <c r="B300" s="21"/>
       <c r="C300" s="22"/>
       <c r="D300" s="22"/>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" s="20"/>
       <c r="B301" s="21"/>
       <c r="C301" s="22"/>
       <c r="D301" s="22"/>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A302" s="20"/>
       <c r="B302" s="21"/>
       <c r="C302" s="22"/>
       <c r="D302" s="22"/>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A303" s="20"/>
       <c r="B303" s="21"/>
       <c r="C303" s="22"/>
       <c r="D303" s="22"/>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A304" s="20"/>
       <c r="B304" s="21"/>
       <c r="C304" s="22"/>
       <c r="D304" s="22"/>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A305" s="20"/>
       <c r="B305" s="21"/>
       <c r="C305" s="22"/>
       <c r="D305" s="22"/>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A306" s="20"/>
       <c r="B306" s="21"/>
       <c r="C306" s="22"/>
       <c r="D306" s="22"/>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A307" s="20"/>
       <c r="B307" s="21"/>
       <c r="C307" s="22"/>
       <c r="D307" s="22"/>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A308" s="20"/>
       <c r="B308" s="21"/>
       <c r="C308" s="22"/>
       <c r="D308" s="22"/>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" s="20"/>
       <c r="B309" s="21"/>
       <c r="C309" s="22"/>
       <c r="D309" s="22"/>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" s="20"/>
       <c r="B310" s="21"/>
       <c r="C310" s="22"/>
       <c r="D310" s="22"/>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" s="20"/>
       <c r="B311" s="21"/>
       <c r="C311" s="22"/>
       <c r="D311" s="22"/>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" s="20"/>
       <c r="B312" s="21"/>
       <c r="C312" s="22"/>
       <c r="D312" s="22"/>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A313" s="20"/>
       <c r="B313" s="21"/>
       <c r="C313" s="22"/>
       <c r="D313" s="22"/>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A314" s="20"/>
       <c r="B314" s="21"/>
       <c r="C314" s="22"/>
       <c r="D314" s="22"/>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A315" s="20"/>
       <c r="B315" s="21"/>
       <c r="C315" s="22"/>
       <c r="D315" s="22"/>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A316" s="20"/>
       <c r="B316" s="21"/>
       <c r="C316" s="22"/>
       <c r="D316" s="22"/>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A317" s="20"/>
       <c r="B317" s="21"/>
       <c r="C317" s="22"/>
       <c r="D317" s="22"/>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A318" s="20"/>
       <c r="B318" s="21"/>
       <c r="C318" s="22"/>
       <c r="D318" s="22"/>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A319" s="20"/>
       <c r="B319" s="21"/>
       <c r="C319" s="22"/>
       <c r="D319" s="22"/>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A320" s="20"/>
       <c r="B320" s="21"/>
       <c r="C320" s="22"/>
       <c r="D320" s="22"/>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" s="20"/>
       <c r="B321" s="21"/>
       <c r="C321" s="22"/>
       <c r="D321" s="22"/>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" s="20"/>
       <c r="B322" s="21"/>
       <c r="C322" s="22"/>
       <c r="D322" s="22"/>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" s="20"/>
       <c r="B323" s="21"/>
       <c r="C323" s="22"/>
       <c r="D323" s="22"/>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" s="20"/>
       <c r="B324" s="21"/>
       <c r="C324" s="22"/>
       <c r="D324" s="22"/>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" s="20"/>
       <c r="B325" s="21"/>
       <c r="C325" s="22"/>
       <c r="D325" s="22"/>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" s="20"/>
       <c r="B326" s="21"/>
       <c r="C326" s="22"/>
       <c r="D326" s="22"/>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" s="20"/>
       <c r="B327" s="21"/>
       <c r="C327" s="22"/>
       <c r="D327" s="22"/>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" s="20"/>
       <c r="B328" s="21"/>
       <c r="C328" s="22"/>
       <c r="D328" s="22"/>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" s="20"/>
       <c r="B329" s="21"/>
       <c r="C329" s="22"/>
       <c r="D329" s="22"/>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A330" s="20"/>
       <c r="B330" s="21"/>
       <c r="C330" s="22"/>
       <c r="D330" s="22"/>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" s="20"/>
       <c r="B331" s="21"/>
       <c r="C331" s="22"/>
       <c r="D331" s="22"/>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" s="20"/>
       <c r="B332" s="21"/>
       <c r="C332" s="22"/>
       <c r="D332" s="22"/>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" s="20"/>
       <c r="B333" s="21"/>
       <c r="C333" s="22"/>
       <c r="D333" s="22"/>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" s="20"/>
       <c r="B334" s="21"/>
       <c r="C334" s="22"/>
       <c r="D334" s="22"/>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" s="20"/>
       <c r="B335" s="21"/>
       <c r="C335" s="22"/>
       <c r="D335" s="22"/>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" s="20"/>
       <c r="B336" s="21"/>
       <c r="C336" s="22"/>
       <c r="D336" s="22"/>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" s="20"/>
       <c r="B337" s="21"/>
       <c r="C337" s="22"/>
       <c r="D337" s="22"/>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" s="20"/>
       <c r="B338" s="21"/>
       <c r="C338" s="22"/>
       <c r="D338" s="22"/>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" s="20"/>
       <c r="B339" s="21"/>
       <c r="C339" s="22"/>
       <c r="D339" s="22"/>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" s="20"/>
       <c r="B340" s="21"/>
       <c r="C340" s="22"/>
       <c r="D340" s="22"/>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" s="20"/>
       <c r="B341" s="21"/>
       <c r="C341" s="22"/>
       <c r="D341" s="22"/>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" s="20"/>
       <c r="B342" s="21"/>
       <c r="C342" s="22"/>
       <c r="D342" s="22"/>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" s="20"/>
       <c r="B343" s="21"/>
       <c r="C343" s="22"/>
       <c r="D343" s="22"/>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" s="20"/>
       <c r="B344" s="21"/>
       <c r="C344" s="22"/>
       <c r="D344" s="22"/>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" s="20"/>
       <c r="B345" s="21"/>
       <c r="C345" s="22"/>
       <c r="D345" s="22"/>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" s="20"/>
       <c r="B346" s="21"/>
       <c r="C346" s="22"/>
       <c r="D346" s="22"/>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" s="20"/>
       <c r="B347" s="21"/>
       <c r="C347" s="22"/>
       <c r="D347" s="22"/>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" s="20"/>
       <c r="B348" s="21"/>
       <c r="C348" s="22"/>
       <c r="D348" s="22"/>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" s="20"/>
       <c r="B349" s="21"/>
       <c r="C349" s="22"/>
       <c r="D349" s="22"/>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" s="20"/>
       <c r="B350" s="21"/>
       <c r="C350" s="22"/>
       <c r="D350" s="22"/>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" s="20"/>
       <c r="B351" s="21"/>
       <c r="C351" s="22"/>
       <c r="D351" s="22"/>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" s="20"/>
       <c r="B352" s="21"/>
       <c r="C352" s="22"/>
       <c r="D352" s="22"/>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" s="20"/>
       <c r="B353" s="21"/>
       <c r="C353" s="22"/>
       <c r="D353" s="22"/>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" s="20"/>
       <c r="B354" s="21"/>
       <c r="C354" s="22"/>
       <c r="D354" s="22"/>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" s="20"/>
       <c r="B355" s="21"/>
       <c r="C355" s="22"/>
       <c r="D355" s="22"/>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" s="20"/>
       <c r="B356" s="21"/>
       <c r="C356" s="22"/>
       <c r="D356" s="22"/>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" s="20"/>
       <c r="B357" s="21"/>
       <c r="C357" s="22"/>
       <c r="D357" s="22"/>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" s="20"/>
       <c r="B358" s="21"/>
       <c r="C358" s="22"/>
       <c r="D358" s="22"/>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" s="20"/>
       <c r="B359" s="21"/>
       <c r="C359" s="22"/>
       <c r="D359" s="22"/>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" s="20"/>
       <c r="B360" s="21"/>
       <c r="C360" s="22"/>
       <c r="D360" s="22"/>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" s="20"/>
       <c r="B361" s="21"/>
       <c r="C361" s="22"/>
       <c r="D361" s="22"/>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" s="20"/>
       <c r="B362" s="21"/>
       <c r="C362" s="22"/>
       <c r="D362" s="22"/>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" s="20"/>
       <c r="B363" s="21"/>
       <c r="C363" s="22"/>
       <c r="D363" s="22"/>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" s="20"/>
       <c r="B364" s="21"/>
       <c r="C364" s="22"/>
       <c r="D364" s="22"/>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" s="20"/>
       <c r="B365" s="21"/>
       <c r="C365" s="22"/>
       <c r="D365" s="22"/>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" s="20"/>
       <c r="B366" s="21"/>
       <c r="C366" s="22"/>
       <c r="D366" s="22"/>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" s="20"/>
       <c r="B367" s="21"/>
       <c r="C367" s="22"/>
       <c r="D367" s="22"/>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" s="20"/>
       <c r="B368" s="21"/>
       <c r="C368" s="22"/>
       <c r="D368" s="22"/>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" s="20"/>
       <c r="B369" s="21"/>
       <c r="C369" s="22"/>
       <c r="D369" s="22"/>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" s="20"/>
       <c r="B370" s="21"/>
       <c r="C370" s="22"/>
       <c r="D370" s="22"/>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" s="20"/>
       <c r="B371" s="21"/>
       <c r="C371" s="22"/>
       <c r="D371" s="22"/>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" s="20"/>
       <c r="B372" s="21"/>
       <c r="C372" s="22"/>
       <c r="D372" s="22"/>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" s="20"/>
       <c r="B373" s="21"/>
       <c r="C373" s="22"/>
       <c r="D373" s="22"/>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" s="20"/>
       <c r="B374" s="21"/>
       <c r="C374" s="22"/>
       <c r="D374" s="22"/>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" s="20"/>
       <c r="B375" s="21"/>
       <c r="C375" s="22"/>
       <c r="D375" s="22"/>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" s="20"/>
       <c r="B376" s="21"/>
       <c r="C376" s="22"/>
       <c r="D376" s="22"/>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" s="20"/>
       <c r="B377" s="21"/>
       <c r="C377" s="22"/>
       <c r="D377" s="22"/>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" s="20"/>
       <c r="B378" s="21"/>
       <c r="C378" s="22"/>
       <c r="D378" s="22"/>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" s="20"/>
       <c r="B379" s="21"/>
       <c r="C379" s="22"/>
       <c r="D379" s="22"/>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" s="20"/>
       <c r="B380" s="21"/>
       <c r="C380" s="22"/>
       <c r="D380" s="22"/>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" s="20"/>
       <c r="B381" s="21"/>
       <c r="C381" s="22"/>
       <c r="D381" s="22"/>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" s="20"/>
       <c r="B382" s="21"/>
       <c r="C382" s="22"/>
       <c r="D382" s="22"/>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" s="20"/>
       <c r="B383" s="21"/>
       <c r="C383" s="22"/>
       <c r="D383" s="22"/>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" s="20"/>
       <c r="B384" s="21"/>
       <c r="C384" s="22"/>
       <c r="D384" s="22"/>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" s="20"/>
       <c r="B385" s="21"/>
       <c r="C385" s="22"/>
       <c r="D385" s="22"/>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" s="20"/>
       <c r="B386" s="21"/>
       <c r="C386" s="22"/>
       <c r="D386" s="22"/>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" s="20"/>
       <c r="B387" s="21"/>
       <c r="C387" s="22"/>
       <c r="D387" s="22"/>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" s="20"/>
       <c r="B388" s="21"/>
       <c r="C388" s="22"/>
       <c r="D388" s="22"/>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" s="20"/>
       <c r="B389" s="21"/>
       <c r="C389" s="22"/>
       <c r="D389" s="22"/>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" s="20"/>
       <c r="B390" s="21"/>
       <c r="C390" s="22"/>
       <c r="D390" s="22"/>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" s="20"/>
       <c r="B391" s="21"/>
       <c r="C391" s="22"/>
       <c r="D391" s="22"/>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" s="20"/>
       <c r="B392" s="21"/>
       <c r="C392" s="22"/>
       <c r="D392" s="22"/>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" s="20"/>
       <c r="B393" s="21"/>
       <c r="C393" s="22"/>
       <c r="D393" s="22"/>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A394" s="20"/>
       <c r="B394" s="21"/>
       <c r="C394" s="22"/>
       <c r="D394" s="22"/>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" s="20"/>
       <c r="B395" s="21"/>
       <c r="C395" s="22"/>
       <c r="D395" s="22"/>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" s="20"/>
       <c r="B396" s="21"/>
       <c r="C396" s="22"/>
       <c r="D396" s="22"/>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" s="20"/>
       <c r="B397" s="21"/>
       <c r="C397" s="22"/>
       <c r="D397" s="22"/>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" s="20"/>
       <c r="B398" s="21"/>
       <c r="C398" s="22"/>
       <c r="D398" s="22"/>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A399" s="20"/>
       <c r="B399" s="21"/>
       <c r="C399" s="22"/>
       <c r="D399" s="22"/>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" s="20"/>
       <c r="B400" s="21"/>
       <c r="C400" s="22"/>
       <c r="D400" s="22"/>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" s="20"/>
       <c r="B401" s="21"/>
       <c r="C401" s="22"/>
       <c r="D401" s="22"/>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" s="20"/>
       <c r="B402" s="21"/>
       <c r="C402" s="22"/>
       <c r="D402" s="22"/>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" s="20"/>
       <c r="B403" s="21"/>
       <c r="C403" s="22"/>
       <c r="D403" s="22"/>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" s="20"/>
       <c r="B404" s="21"/>
       <c r="C404" s="22"/>
       <c r="D404" s="22"/>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" s="20"/>
       <c r="B405" s="21"/>
       <c r="C405" s="22"/>
       <c r="D405" s="22"/>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" s="20"/>
       <c r="B406" s="21"/>
       <c r="C406" s="22"/>
       <c r="D406" s="22"/>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A407" s="20"/>
       <c r="B407" s="21"/>
       <c r="C407" s="22"/>
       <c r="D407" s="22"/>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A408" s="20"/>
       <c r="B408" s="21"/>
       <c r="C408" s="22"/>
       <c r="D408" s="22"/>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" s="20"/>
       <c r="B409" s="21"/>
       <c r="C409" s="22"/>
       <c r="D409" s="22"/>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" s="20"/>
       <c r="B410" s="21"/>
       <c r="C410" s="22"/>
       <c r="D410" s="22"/>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" s="20"/>
       <c r="B411" s="21"/>
       <c r="C411" s="22"/>
       <c r="D411" s="22"/>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A412" s="20"/>
       <c r="B412" s="21"/>
       <c r="C412" s="22"/>
       <c r="D412" s="22"/>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" s="20"/>
       <c r="B413" s="21"/>
       <c r="C413" s="22"/>
       <c r="D413" s="22"/>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" s="20"/>
       <c r="B414" s="21"/>
       <c r="C414" s="22"/>
       <c r="D414" s="22"/>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" s="20"/>
       <c r="B415" s="21"/>
       <c r="C415" s="22"/>
       <c r="D415" s="22"/>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" s="20"/>
       <c r="B416" s="21"/>
       <c r="C416" s="22"/>
       <c r="D416" s="22"/>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" s="20"/>
       <c r="B417" s="21"/>
       <c r="C417" s="22"/>
       <c r="D417" s="22"/>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" s="20"/>
       <c r="B418" s="21"/>
       <c r="C418" s="22"/>
       <c r="D418" s="22"/>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" s="20"/>
       <c r="B419" s="21"/>
       <c r="C419" s="22"/>
       <c r="D419" s="22"/>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A420" s="20"/>
       <c r="B420" s="21"/>
       <c r="C420" s="22"/>
       <c r="D420" s="22"/>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A421" s="20"/>
       <c r="B421" s="21"/>
       <c r="C421" s="22"/>
       <c r="D421" s="22"/>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A422" s="20"/>
       <c r="B422" s="21"/>
       <c r="C422" s="22"/>
       <c r="D422" s="22"/>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" s="20"/>
       <c r="B423" s="21"/>
       <c r="C423" s="22"/>
       <c r="D423" s="22"/>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" s="20"/>
       <c r="B424" s="21"/>
       <c r="C424" s="22"/>
       <c r="D424" s="22"/>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" s="20"/>
       <c r="B425" s="21"/>
       <c r="C425" s="22"/>
       <c r="D425" s="22"/>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" s="20"/>
       <c r="B426" s="21"/>
       <c r="C426" s="22"/>
       <c r="D426" s="22"/>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" s="20"/>
       <c r="B427" s="21"/>
       <c r="C427" s="22"/>
       <c r="D427" s="22"/>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" s="20"/>
       <c r="B428" s="21"/>
       <c r="C428" s="22"/>
       <c r="D428" s="22"/>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" s="20"/>
       <c r="B429" s="21"/>
       <c r="C429" s="22"/>
       <c r="D429" s="22"/>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" s="20"/>
       <c r="B430" s="21"/>
       <c r="C430" s="22"/>
       <c r="D430" s="22"/>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" s="20"/>
       <c r="B431" s="21"/>
       <c r="C431" s="22"/>
       <c r="D431" s="22"/>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" s="20"/>
       <c r="B432" s="21"/>
       <c r="C432" s="22"/>
       <c r="D432" s="22"/>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A433" s="20"/>
       <c r="B433" s="21"/>
       <c r="C433" s="22"/>
       <c r="D433" s="22"/>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" s="20"/>
       <c r="B434" s="21"/>
       <c r="C434" s="22"/>
       <c r="D434" s="22"/>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" s="20"/>
       <c r="B435" s="21"/>
       <c r="C435" s="22"/>
       <c r="D435" s="22"/>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" s="20"/>
       <c r="B436" s="21"/>
       <c r="C436" s="22"/>
       <c r="D436" s="22"/>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" s="20"/>
       <c r="B437" s="21"/>
       <c r="C437" s="22"/>
       <c r="D437" s="22"/>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" s="20"/>
       <c r="B438" s="21"/>
       <c r="C438" s="22"/>
       <c r="D438" s="22"/>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" s="20"/>
       <c r="B439" s="21"/>
       <c r="C439" s="22"/>
       <c r="D439" s="22"/>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A440" s="20"/>
       <c r="B440" s="21"/>
       <c r="C440" s="22"/>
       <c r="D440" s="22"/>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" s="20"/>
       <c r="B441" s="21"/>
       <c r="C441" s="22"/>
       <c r="D441" s="22"/>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" s="20"/>
       <c r="B442" s="21"/>
       <c r="C442" s="22"/>
       <c r="D442" s="22"/>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" s="20"/>
       <c r="B443" s="21"/>
       <c r="C443" s="22"/>
       <c r="D443" s="22"/>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" s="20"/>
       <c r="B444" s="21"/>
       <c r="C444" s="22"/>
       <c r="D444" s="22"/>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" s="20"/>
       <c r="B445" s="21"/>
       <c r="C445" s="22"/>
       <c r="D445" s="22"/>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" s="20"/>
       <c r="B446" s="21"/>
       <c r="C446" s="22"/>
       <c r="D446" s="22"/>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A447" s="20"/>
       <c r="B447" s="21"/>
       <c r="C447" s="22"/>
       <c r="D447" s="22"/>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" s="20"/>
       <c r="B448" s="21"/>
       <c r="C448" s="22"/>
       <c r="D448" s="22"/>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" s="20"/>
       <c r="B449" s="21"/>
       <c r="C449" s="22"/>
       <c r="D449" s="22"/>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" s="20"/>
       <c r="B450" s="21"/>
       <c r="C450" s="22"/>
       <c r="D450" s="22"/>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" s="20"/>
       <c r="B451" s="21"/>
       <c r="C451" s="22"/>
       <c r="D451" s="22"/>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" s="20"/>
       <c r="B452" s="21"/>
       <c r="C452" s="22"/>
       <c r="D452" s="22"/>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" s="20"/>
       <c r="B453" s="21"/>
       <c r="C453" s="22"/>
       <c r="D453" s="22"/>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" s="20"/>
       <c r="B454" s="21"/>
       <c r="C454" s="22"/>
       <c r="D454" s="22"/>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" s="20"/>
       <c r="B455" s="21"/>
       <c r="C455" s="22"/>
       <c r="D455" s="22"/>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A456" s="20"/>
       <c r="B456" s="21"/>
       <c r="C456" s="22"/>
       <c r="D456" s="22"/>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" s="20"/>
       <c r="B457" s="21"/>
       <c r="C457" s="22"/>
       <c r="D457" s="22"/>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A458" s="20"/>
       <c r="B458" s="21"/>
       <c r="C458" s="22"/>
       <c r="D458" s="22"/>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" s="20"/>
       <c r="B459" s="21"/>
       <c r="C459" s="22"/>
       <c r="D459" s="22"/>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" s="20"/>
       <c r="B460" s="21"/>
       <c r="C460" s="22"/>
       <c r="D460" s="22"/>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" s="20"/>
       <c r="B461" s="21"/>
       <c r="C461" s="22"/>
       <c r="D461" s="22"/>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" s="20"/>
       <c r="B462" s="21"/>
       <c r="C462" s="22"/>
       <c r="D462" s="22"/>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" s="20"/>
       <c r="B463" s="21"/>
       <c r="C463" s="22"/>
       <c r="D463" s="22"/>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" s="20"/>
       <c r="B464" s="21"/>
       <c r="C464" s="22"/>
       <c r="D464" s="22"/>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" s="20"/>
       <c r="B465" s="21"/>
       <c r="C465" s="22"/>
       <c r="D465" s="22"/>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" s="20"/>
       <c r="B466" s="21"/>
       <c r="C466" s="22"/>
       <c r="D466" s="22"/>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" s="20"/>
       <c r="B467" s="21"/>
       <c r="C467" s="22"/>
       <c r="D467" s="22"/>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" s="20"/>
       <c r="B468" s="21"/>
       <c r="C468" s="22"/>
       <c r="D468" s="22"/>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A469" s="20"/>
       <c r="B469" s="21"/>
       <c r="C469" s="22"/>
       <c r="D469" s="22"/>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A470" s="20"/>
       <c r="B470" s="21"/>
       <c r="C470" s="22"/>
       <c r="D470" s="22"/>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" s="20"/>
       <c r="B471" s="21"/>
       <c r="C471" s="22"/>
       <c r="D471" s="22"/>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" s="20"/>
       <c r="B472" s="21"/>
       <c r="C472" s="22"/>
       <c r="D472" s="22"/>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" s="20"/>
       <c r="B473" s="21"/>
       <c r="C473" s="22"/>
       <c r="D473" s="22"/>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" s="20"/>
       <c r="B474" s="21"/>
       <c r="C474" s="22"/>
       <c r="D474" s="22"/>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" s="20"/>
       <c r="B475" s="21"/>
       <c r="C475" s="22"/>
       <c r="D475" s="22"/>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" s="20"/>
       <c r="B476" s="21"/>
       <c r="C476" s="22"/>
       <c r="D476" s="22"/>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" s="20"/>
       <c r="B477" s="21"/>
       <c r="C477" s="22"/>
       <c r="D477" s="22"/>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" s="20"/>
       <c r="B478" s="21"/>
       <c r="C478" s="22"/>
       <c r="D478" s="22"/>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A479" s="20"/>
       <c r="B479" s="21"/>
       <c r="C479" s="22"/>
       <c r="D479" s="22"/>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A480" s="20"/>
       <c r="B480" s="21"/>
       <c r="C480" s="22"/>
       <c r="D480" s="22"/>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A481" s="20"/>
       <c r="B481" s="21"/>
       <c r="C481" s="22"/>
       <c r="D481" s="22"/>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" s="20"/>
       <c r="B482" s="21"/>
       <c r="C482" s="22"/>
       <c r="D482" s="22"/>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" s="20"/>
       <c r="B483" s="21"/>
       <c r="C483" s="22"/>
       <c r="D483" s="22"/>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" s="20"/>
       <c r="B484" s="21"/>
       <c r="C484" s="22"/>
       <c r="D484" s="22"/>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A485" s="20"/>
       <c r="B485" s="21"/>
       <c r="C485" s="22"/>
       <c r="D485" s="22"/>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" s="20"/>
       <c r="B486" s="21"/>
       <c r="C486" s="22"/>
       <c r="D486" s="22"/>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" s="20"/>
       <c r="B487" s="21"/>
       <c r="C487" s="22"/>
       <c r="D487" s="22"/>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" s="20"/>
       <c r="B488" s="21"/>
       <c r="C488" s="22"/>
       <c r="D488" s="22"/>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" s="20"/>
       <c r="B489" s="21"/>
       <c r="C489" s="22"/>
       <c r="D489" s="22"/>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A490" s="20"/>
       <c r="B490" s="21"/>
       <c r="C490" s="22"/>
       <c r="D490" s="22"/>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A491" s="20"/>
       <c r="B491" s="21"/>
       <c r="C491" s="22"/>
       <c r="D491" s="22"/>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" s="20"/>
       <c r="B492" s="21"/>
       <c r="C492" s="22"/>
       <c r="D492" s="22"/>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" s="20"/>
       <c r="B493" s="21"/>
       <c r="C493" s="22"/>
       <c r="D493" s="22"/>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" s="20"/>
       <c r="B494" s="21"/>
       <c r="C494" s="22"/>
       <c r="D494" s="22"/>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" s="20"/>
       <c r="B495" s="21"/>
       <c r="C495" s="22"/>
       <c r="D495" s="22"/>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" s="20"/>
       <c r="B496" s="21"/>
       <c r="C496" s="22"/>
       <c r="D496" s="22"/>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A497" s="20"/>
       <c r="B497" s="21"/>
       <c r="C497" s="22"/>
       <c r="D497" s="22"/>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A498" s="20"/>
       <c r="B498" s="21"/>
       <c r="C498" s="22"/>
       <c r="D498" s="22"/>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A499" s="20"/>
       <c r="B499" s="21"/>
       <c r="C499" s="22"/>
       <c r="D499" s="22"/>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A500" s="20"/>
       <c r="B500" s="21"/>
       <c r="C500" s="22"/>
       <c r="D500" s="22"/>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A501" s="20"/>
       <c r="B501" s="21"/>
       <c r="C501" s="22"/>
@@ -6475,7 +6567,7 @@
       <formula1>"Producer,Game Designer,Technical Director,Programmer,QA,Einarbeitung / Lernen"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" sqref="B2:B501" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="decimal" allowBlank="1" sqref="B2:B5 B7:B501" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>0</formula1>
       <formula2>16</formula2>
     </dataValidation>
@@ -6488,7 +6580,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P201"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -6506,7 +6598,7 @@
     <col min="16" max="16" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>72</v>
       </c>
@@ -6556,7 +6648,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="39" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>88</v>
       </c>
@@ -6606,7 +6698,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -6630,7 +6722,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="22"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="22"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -6654,7 +6746,7 @@
       <c r="O4" s="22"/>
       <c r="P4" s="22"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="22"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
@@ -6678,7 +6770,7 @@
       <c r="O5" s="22"/>
       <c r="P5" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="22"/>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
@@ -6702,7 +6794,7 @@
       <c r="O6" s="22"/>
       <c r="P6" s="22"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="22"/>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -6726,7 +6818,7 @@
       <c r="O7" s="22"/>
       <c r="P7" s="22"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="22"/>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -6750,7 +6842,7 @@
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="22"/>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -6774,7 +6866,7 @@
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
@@ -6798,7 +6890,7 @@
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="22"/>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -6822,7 +6914,7 @@
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="22"/>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -6846,7 +6938,7 @@
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="22"/>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
@@ -6870,7 +6962,7 @@
       <c r="O13" s="22"/>
       <c r="P13" s="22"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="22"/>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -6894,7 +6986,7 @@
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="22"/>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -6918,7 +7010,7 @@
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -6942,7 +7034,7 @@
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="22"/>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -6966,7 +7058,7 @@
       <c r="O17" s="22"/>
       <c r="P17" s="22"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="22"/>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -6990,7 +7082,7 @@
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="22"/>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -7014,7 +7106,7 @@
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -7038,7 +7130,7 @@
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
@@ -7062,7 +7154,7 @@
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="22"/>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -7086,7 +7178,7 @@
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -7110,7 +7202,7 @@
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -7134,7 +7226,7 @@
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -7158,7 +7250,7 @@
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -7182,7 +7274,7 @@
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="22"/>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -7206,7 +7298,7 @@
       <c r="O27" s="22"/>
       <c r="P27" s="22"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -7230,7 +7322,7 @@
       <c r="O28" s="22"/>
       <c r="P28" s="22"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -7254,7 +7346,7 @@
       <c r="O29" s="22"/>
       <c r="P29" s="22"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
@@ -7278,7 +7370,7 @@
       <c r="O30" s="22"/>
       <c r="P30" s="22"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -7302,7 +7394,7 @@
       <c r="O31" s="22"/>
       <c r="P31" s="22"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
@@ -7326,7 +7418,7 @@
       <c r="O32" s="22"/>
       <c r="P32" s="22"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
@@ -7350,7 +7442,7 @@
       <c r="O33" s="22"/>
       <c r="P33" s="22"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
@@ -7374,7 +7466,7 @@
       <c r="O34" s="22"/>
       <c r="P34" s="22"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="22"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
@@ -7398,7 +7490,7 @@
       <c r="O35" s="22"/>
       <c r="P35" s="22"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="22"/>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -7422,7 +7514,7 @@
       <c r="O36" s="22"/>
       <c r="P36" s="22"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="22"/>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
@@ -7446,7 +7538,7 @@
       <c r="O37" s="22"/>
       <c r="P37" s="22"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="22"/>
       <c r="B38" s="22"/>
       <c r="C38" s="22"/>
@@ -7470,7 +7562,7 @@
       <c r="O38" s="22"/>
       <c r="P38" s="22"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="22"/>
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
@@ -7494,7 +7586,7 @@
       <c r="O39" s="22"/>
       <c r="P39" s="22"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="22"/>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -7518,7 +7610,7 @@
       <c r="O40" s="22"/>
       <c r="P40" s="22"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="22"/>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -7542,7 +7634,7 @@
       <c r="O41" s="22"/>
       <c r="P41" s="22"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="22"/>
       <c r="B42" s="22"/>
       <c r="C42" s="22"/>
@@ -7566,7 +7658,7 @@
       <c r="O42" s="22"/>
       <c r="P42" s="22"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="22"/>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
@@ -7590,7 +7682,7 @@
       <c r="O43" s="22"/>
       <c r="P43" s="22"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="22"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -7614,7 +7706,7 @@
       <c r="O44" s="22"/>
       <c r="P44" s="22"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="22"/>
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
@@ -7638,7 +7730,7 @@
       <c r="O45" s="22"/>
       <c r="P45" s="22"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="22"/>
       <c r="B46" s="22"/>
       <c r="C46" s="22"/>
@@ -7662,7 +7754,7 @@
       <c r="O46" s="22"/>
       <c r="P46" s="22"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="22"/>
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
@@ -7686,7 +7778,7 @@
       <c r="O47" s="22"/>
       <c r="P47" s="22"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="22"/>
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
@@ -7710,7 +7802,7 @@
       <c r="O48" s="22"/>
       <c r="P48" s="22"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="22"/>
       <c r="B49" s="22"/>
       <c r="C49" s="22"/>
@@ -7734,7 +7826,7 @@
       <c r="O49" s="22"/>
       <c r="P49" s="22"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="22"/>
       <c r="B50" s="22"/>
       <c r="C50" s="22"/>
@@ -7758,7 +7850,7 @@
       <c r="O50" s="22"/>
       <c r="P50" s="22"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="22"/>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
@@ -7782,7 +7874,7 @@
       <c r="O51" s="22"/>
       <c r="P51" s="22"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="22"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -7806,7 +7898,7 @@
       <c r="O52" s="22"/>
       <c r="P52" s="22"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="22"/>
       <c r="B53" s="22"/>
       <c r="C53" s="22"/>
@@ -7830,7 +7922,7 @@
       <c r="O53" s="22"/>
       <c r="P53" s="22"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="22"/>
       <c r="B54" s="22"/>
       <c r="C54" s="22"/>
@@ -7854,7 +7946,7 @@
       <c r="O54" s="22"/>
       <c r="P54" s="22"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="22"/>
       <c r="B55" s="22"/>
       <c r="C55" s="22"/>
@@ -7878,7 +7970,7 @@
       <c r="O55" s="22"/>
       <c r="P55" s="22"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="22"/>
       <c r="B56" s="22"/>
       <c r="C56" s="22"/>
@@ -7902,7 +7994,7 @@
       <c r="O56" s="22"/>
       <c r="P56" s="22"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="22"/>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
@@ -7926,7 +8018,7 @@
       <c r="O57" s="22"/>
       <c r="P57" s="22"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="22"/>
       <c r="B58" s="22"/>
       <c r="C58" s="22"/>
@@ -7950,7 +8042,7 @@
       <c r="O58" s="22"/>
       <c r="P58" s="22"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="22"/>
       <c r="B59" s="22"/>
       <c r="C59" s="22"/>
@@ -7974,7 +8066,7 @@
       <c r="O59" s="22"/>
       <c r="P59" s="22"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="22"/>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -7998,7 +8090,7 @@
       <c r="O60" s="22"/>
       <c r="P60" s="22"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="22"/>
       <c r="B61" s="22"/>
       <c r="C61" s="22"/>
@@ -8022,7 +8114,7 @@
       <c r="O61" s="22"/>
       <c r="P61" s="22"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="22"/>
       <c r="B62" s="22"/>
       <c r="C62" s="22"/>
@@ -8046,7 +8138,7 @@
       <c r="O62" s="22"/>
       <c r="P62" s="22"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="22"/>
       <c r="B63" s="22"/>
       <c r="C63" s="22"/>
@@ -8070,7 +8162,7 @@
       <c r="O63" s="22"/>
       <c r="P63" s="22"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="22"/>
       <c r="B64" s="22"/>
       <c r="C64" s="22"/>
@@ -8094,7 +8186,7 @@
       <c r="O64" s="22"/>
       <c r="P64" s="22"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="22"/>
       <c r="B65" s="22"/>
       <c r="C65" s="22"/>
@@ -8118,7 +8210,7 @@
       <c r="O65" s="22"/>
       <c r="P65" s="22"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="22"/>
       <c r="B66" s="22"/>
       <c r="C66" s="22"/>
@@ -8142,7 +8234,7 @@
       <c r="O66" s="22"/>
       <c r="P66" s="22"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="22"/>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -8166,7 +8258,7 @@
       <c r="O67" s="22"/>
       <c r="P67" s="22"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="22"/>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -8190,7 +8282,7 @@
       <c r="O68" s="22"/>
       <c r="P68" s="22"/>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="22"/>
       <c r="B69" s="22"/>
       <c r="C69" s="22"/>
@@ -8214,7 +8306,7 @@
       <c r="O69" s="22"/>
       <c r="P69" s="22"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" s="22"/>
       <c r="B70" s="22"/>
       <c r="C70" s="22"/>
@@ -8238,7 +8330,7 @@
       <c r="O70" s="22"/>
       <c r="P70" s="22"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" s="22"/>
       <c r="B71" s="22"/>
       <c r="C71" s="22"/>
@@ -8262,7 +8354,7 @@
       <c r="O71" s="22"/>
       <c r="P71" s="22"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" s="22"/>
       <c r="B72" s="22"/>
       <c r="C72" s="22"/>
@@ -8286,7 +8378,7 @@
       <c r="O72" s="22"/>
       <c r="P72" s="22"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" s="22"/>
       <c r="B73" s="22"/>
       <c r="C73" s="22"/>
@@ -8310,7 +8402,7 @@
       <c r="O73" s="22"/>
       <c r="P73" s="22"/>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="22"/>
       <c r="B74" s="22"/>
       <c r="C74" s="22"/>
@@ -8334,7 +8426,7 @@
       <c r="O74" s="22"/>
       <c r="P74" s="22"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" s="22"/>
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
@@ -8358,7 +8450,7 @@
       <c r="O75" s="22"/>
       <c r="P75" s="22"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" s="22"/>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -8382,7 +8474,7 @@
       <c r="O76" s="22"/>
       <c r="P76" s="22"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" s="22"/>
       <c r="B77" s="22"/>
       <c r="C77" s="22"/>
@@ -8406,7 +8498,7 @@
       <c r="O77" s="22"/>
       <c r="P77" s="22"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" s="22"/>
       <c r="B78" s="22"/>
       <c r="C78" s="22"/>
@@ -8430,7 +8522,7 @@
       <c r="O78" s="22"/>
       <c r="P78" s="22"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" s="22"/>
       <c r="B79" s="22"/>
       <c r="C79" s="22"/>
@@ -8454,7 +8546,7 @@
       <c r="O79" s="22"/>
       <c r="P79" s="22"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" s="22"/>
       <c r="B80" s="22"/>
       <c r="C80" s="22"/>
@@ -8478,7 +8570,7 @@
       <c r="O80" s="22"/>
       <c r="P80" s="22"/>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" s="22"/>
       <c r="B81" s="22"/>
       <c r="C81" s="22"/>
@@ -8502,7 +8594,7 @@
       <c r="O81" s="22"/>
       <c r="P81" s="22"/>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" s="22"/>
       <c r="B82" s="22"/>
       <c r="C82" s="22"/>
@@ -8526,7 +8618,7 @@
       <c r="O82" s="22"/>
       <c r="P82" s="22"/>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" s="22"/>
       <c r="B83" s="22"/>
       <c r="C83" s="22"/>
@@ -8550,7 +8642,7 @@
       <c r="O83" s="22"/>
       <c r="P83" s="22"/>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" s="22"/>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -8574,7 +8666,7 @@
       <c r="O84" s="22"/>
       <c r="P84" s="22"/>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" s="22"/>
       <c r="B85" s="22"/>
       <c r="C85" s="22"/>
@@ -8598,7 +8690,7 @@
       <c r="O85" s="22"/>
       <c r="P85" s="22"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="22"/>
       <c r="B86" s="22"/>
       <c r="C86" s="22"/>
@@ -8622,7 +8714,7 @@
       <c r="O86" s="22"/>
       <c r="P86" s="22"/>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" s="22"/>
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
@@ -8646,7 +8738,7 @@
       <c r="O87" s="22"/>
       <c r="P87" s="22"/>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="22"/>
       <c r="B88" s="22"/>
       <c r="C88" s="22"/>
@@ -8670,7 +8762,7 @@
       <c r="O88" s="22"/>
       <c r="P88" s="22"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="22"/>
       <c r="B89" s="22"/>
       <c r="C89" s="22"/>
@@ -8694,7 +8786,7 @@
       <c r="O89" s="22"/>
       <c r="P89" s="22"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="22"/>
       <c r="B90" s="22"/>
       <c r="C90" s="22"/>
@@ -8718,7 +8810,7 @@
       <c r="O90" s="22"/>
       <c r="P90" s="22"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" s="22"/>
       <c r="B91" s="22"/>
       <c r="C91" s="22"/>
@@ -8742,7 +8834,7 @@
       <c r="O91" s="22"/>
       <c r="P91" s="22"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" s="22"/>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -8766,7 +8858,7 @@
       <c r="O92" s="22"/>
       <c r="P92" s="22"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" s="22"/>
       <c r="B93" s="22"/>
       <c r="C93" s="22"/>
@@ -8790,7 +8882,7 @@
       <c r="O93" s="22"/>
       <c r="P93" s="22"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" s="22"/>
       <c r="B94" s="22"/>
       <c r="C94" s="22"/>
@@ -8814,7 +8906,7 @@
       <c r="O94" s="22"/>
       <c r="P94" s="22"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" s="22"/>
       <c r="B95" s="22"/>
       <c r="C95" s="22"/>
@@ -8838,7 +8930,7 @@
       <c r="O95" s="22"/>
       <c r="P95" s="22"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" s="22"/>
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
@@ -8862,7 +8954,7 @@
       <c r="O96" s="22"/>
       <c r="P96" s="22"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" s="22"/>
       <c r="B97" s="22"/>
       <c r="C97" s="22"/>
@@ -8886,7 +8978,7 @@
       <c r="O97" s="22"/>
       <c r="P97" s="22"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" s="22"/>
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
@@ -8910,7 +9002,7 @@
       <c r="O98" s="22"/>
       <c r="P98" s="22"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" s="22"/>
       <c r="B99" s="22"/>
       <c r="C99" s="22"/>
@@ -8934,7 +9026,7 @@
       <c r="O99" s="22"/>
       <c r="P99" s="22"/>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" s="22"/>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -8958,7 +9050,7 @@
       <c r="O100" s="22"/>
       <c r="P100" s="22"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" s="22"/>
       <c r="B101" s="22"/>
       <c r="C101" s="22"/>
@@ -8982,7 +9074,7 @@
       <c r="O101" s="22"/>
       <c r="P101" s="22"/>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" s="22"/>
       <c r="B102" s="22"/>
       <c r="C102" s="22"/>
@@ -9006,7 +9098,7 @@
       <c r="O102" s="22"/>
       <c r="P102" s="22"/>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" s="22"/>
       <c r="B103" s="22"/>
       <c r="C103" s="22"/>
@@ -9030,7 +9122,7 @@
       <c r="O103" s="22"/>
       <c r="P103" s="22"/>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" s="22"/>
       <c r="B104" s="22"/>
       <c r="C104" s="22"/>
@@ -9054,7 +9146,7 @@
       <c r="O104" s="22"/>
       <c r="P104" s="22"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" s="22"/>
       <c r="B105" s="22"/>
       <c r="C105" s="22"/>
@@ -9078,7 +9170,7 @@
       <c r="O105" s="22"/>
       <c r="P105" s="22"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" s="22"/>
       <c r="B106" s="22"/>
       <c r="C106" s="22"/>
@@ -9102,7 +9194,7 @@
       <c r="O106" s="22"/>
       <c r="P106" s="22"/>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" s="22"/>
       <c r="B107" s="22"/>
       <c r="C107" s="22"/>
@@ -9126,7 +9218,7 @@
       <c r="O107" s="22"/>
       <c r="P107" s="22"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" s="22"/>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
@@ -9150,7 +9242,7 @@
       <c r="O108" s="22"/>
       <c r="P108" s="22"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" s="22"/>
       <c r="B109" s="22"/>
       <c r="C109" s="22"/>
@@ -9174,7 +9266,7 @@
       <c r="O109" s="22"/>
       <c r="P109" s="22"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" s="22"/>
       <c r="B110" s="22"/>
       <c r="C110" s="22"/>
@@ -9198,7 +9290,7 @@
       <c r="O110" s="22"/>
       <c r="P110" s="22"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" s="22"/>
       <c r="B111" s="22"/>
       <c r="C111" s="22"/>
@@ -9222,7 +9314,7 @@
       <c r="O111" s="22"/>
       <c r="P111" s="22"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" s="22"/>
       <c r="B112" s="22"/>
       <c r="C112" s="22"/>
@@ -9246,7 +9338,7 @@
       <c r="O112" s="22"/>
       <c r="P112" s="22"/>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" s="22"/>
       <c r="B113" s="22"/>
       <c r="C113" s="22"/>
@@ -9270,7 +9362,7 @@
       <c r="O113" s="22"/>
       <c r="P113" s="22"/>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" s="22"/>
       <c r="B114" s="22"/>
       <c r="C114" s="22"/>
@@ -9294,7 +9386,7 @@
       <c r="O114" s="22"/>
       <c r="P114" s="22"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" s="22"/>
       <c r="B115" s="22"/>
       <c r="C115" s="22"/>
@@ -9318,7 +9410,7 @@
       <c r="O115" s="22"/>
       <c r="P115" s="22"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" s="22"/>
       <c r="B116" s="22"/>
       <c r="C116" s="22"/>
@@ -9342,7 +9434,7 @@
       <c r="O116" s="22"/>
       <c r="P116" s="22"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" s="22"/>
       <c r="B117" s="22"/>
       <c r="C117" s="22"/>
@@ -9366,7 +9458,7 @@
       <c r="O117" s="22"/>
       <c r="P117" s="22"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" s="22"/>
       <c r="B118" s="22"/>
       <c r="C118" s="22"/>
@@ -9390,7 +9482,7 @@
       <c r="O118" s="22"/>
       <c r="P118" s="22"/>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119" s="22"/>
       <c r="B119" s="22"/>
       <c r="C119" s="22"/>
@@ -9414,7 +9506,7 @@
       <c r="O119" s="22"/>
       <c r="P119" s="22"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" s="22"/>
       <c r="B120" s="22"/>
       <c r="C120" s="22"/>
@@ -9438,7 +9530,7 @@
       <c r="O120" s="22"/>
       <c r="P120" s="22"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" s="22"/>
       <c r="B121" s="22"/>
       <c r="C121" s="22"/>
@@ -9462,7 +9554,7 @@
       <c r="O121" s="22"/>
       <c r="P121" s="22"/>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122" s="22"/>
       <c r="B122" s="22"/>
       <c r="C122" s="22"/>
@@ -9486,7 +9578,7 @@
       <c r="O122" s="22"/>
       <c r="P122" s="22"/>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123" s="22"/>
       <c r="B123" s="22"/>
       <c r="C123" s="22"/>
@@ -9510,7 +9602,7 @@
       <c r="O123" s="22"/>
       <c r="P123" s="22"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" s="22"/>
       <c r="B124" s="22"/>
       <c r="C124" s="22"/>
@@ -9534,7 +9626,7 @@
       <c r="O124" s="22"/>
       <c r="P124" s="22"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" s="22"/>
       <c r="B125" s="22"/>
       <c r="C125" s="22"/>
@@ -9558,7 +9650,7 @@
       <c r="O125" s="22"/>
       <c r="P125" s="22"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126" s="22"/>
       <c r="B126" s="22"/>
       <c r="C126" s="22"/>
@@ -9582,7 +9674,7 @@
       <c r="O126" s="22"/>
       <c r="P126" s="22"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127" s="22"/>
       <c r="B127" s="22"/>
       <c r="C127" s="22"/>
@@ -9606,7 +9698,7 @@
       <c r="O127" s="22"/>
       <c r="P127" s="22"/>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128" s="22"/>
       <c r="B128" s="22"/>
       <c r="C128" s="22"/>
@@ -9630,7 +9722,7 @@
       <c r="O128" s="22"/>
       <c r="P128" s="22"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" s="22"/>
       <c r="B129" s="22"/>
       <c r="C129" s="22"/>
@@ -9654,7 +9746,7 @@
       <c r="O129" s="22"/>
       <c r="P129" s="22"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" s="22"/>
       <c r="B130" s="22"/>
       <c r="C130" s="22"/>
@@ -9678,7 +9770,7 @@
       <c r="O130" s="22"/>
       <c r="P130" s="22"/>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" s="22"/>
       <c r="B131" s="22"/>
       <c r="C131" s="22"/>
@@ -9702,7 +9794,7 @@
       <c r="O131" s="22"/>
       <c r="P131" s="22"/>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" s="22"/>
       <c r="B132" s="22"/>
       <c r="C132" s="22"/>
@@ -9726,7 +9818,7 @@
       <c r="O132" s="22"/>
       <c r="P132" s="22"/>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" s="22"/>
       <c r="B133" s="22"/>
       <c r="C133" s="22"/>
@@ -9750,7 +9842,7 @@
       <c r="O133" s="22"/>
       <c r="P133" s="22"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" s="22"/>
       <c r="B134" s="22"/>
       <c r="C134" s="22"/>
@@ -9774,7 +9866,7 @@
       <c r="O134" s="22"/>
       <c r="P134" s="22"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" s="22"/>
       <c r="B135" s="22"/>
       <c r="C135" s="22"/>
@@ -9798,7 +9890,7 @@
       <c r="O135" s="22"/>
       <c r="P135" s="22"/>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" s="22"/>
       <c r="B136" s="22"/>
       <c r="C136" s="22"/>
@@ -9822,7 +9914,7 @@
       <c r="O136" s="22"/>
       <c r="P136" s="22"/>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" s="22"/>
       <c r="B137" s="22"/>
       <c r="C137" s="22"/>
@@ -9846,7 +9938,7 @@
       <c r="O137" s="22"/>
       <c r="P137" s="22"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" s="22"/>
       <c r="B138" s="22"/>
       <c r="C138" s="22"/>
@@ -9870,7 +9962,7 @@
       <c r="O138" s="22"/>
       <c r="P138" s="22"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" s="22"/>
       <c r="B139" s="22"/>
       <c r="C139" s="22"/>
@@ -9894,7 +9986,7 @@
       <c r="O139" s="22"/>
       <c r="P139" s="22"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" s="22"/>
       <c r="B140" s="22"/>
       <c r="C140" s="22"/>
@@ -9918,7 +10010,7 @@
       <c r="O140" s="22"/>
       <c r="P140" s="22"/>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" s="22"/>
       <c r="B141" s="22"/>
       <c r="C141" s="22"/>
@@ -9942,7 +10034,7 @@
       <c r="O141" s="22"/>
       <c r="P141" s="22"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" s="22"/>
       <c r="B142" s="22"/>
       <c r="C142" s="22"/>
@@ -9966,7 +10058,7 @@
       <c r="O142" s="22"/>
       <c r="P142" s="22"/>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" s="22"/>
       <c r="B143" s="22"/>
       <c r="C143" s="22"/>
@@ -9990,7 +10082,7 @@
       <c r="O143" s="22"/>
       <c r="P143" s="22"/>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" s="22"/>
       <c r="B144" s="22"/>
       <c r="C144" s="22"/>
@@ -10014,7 +10106,7 @@
       <c r="O144" s="22"/>
       <c r="P144" s="22"/>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" s="22"/>
       <c r="B145" s="22"/>
       <c r="C145" s="22"/>
@@ -10038,7 +10130,7 @@
       <c r="O145" s="22"/>
       <c r="P145" s="22"/>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" s="22"/>
       <c r="B146" s="22"/>
       <c r="C146" s="22"/>
@@ -10062,7 +10154,7 @@
       <c r="O146" s="22"/>
       <c r="P146" s="22"/>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" s="22"/>
       <c r="B147" s="22"/>
       <c r="C147" s="22"/>
@@ -10086,7 +10178,7 @@
       <c r="O147" s="22"/>
       <c r="P147" s="22"/>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" s="22"/>
       <c r="B148" s="22"/>
       <c r="C148" s="22"/>
@@ -10110,7 +10202,7 @@
       <c r="O148" s="22"/>
       <c r="P148" s="22"/>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" s="22"/>
       <c r="B149" s="22"/>
       <c r="C149" s="22"/>
@@ -10134,7 +10226,7 @@
       <c r="O149" s="22"/>
       <c r="P149" s="22"/>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" s="22"/>
       <c r="B150" s="22"/>
       <c r="C150" s="22"/>
@@ -10158,7 +10250,7 @@
       <c r="O150" s="22"/>
       <c r="P150" s="22"/>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151" s="22"/>
       <c r="B151" s="22"/>
       <c r="C151" s="22"/>
@@ -10182,7 +10274,7 @@
       <c r="O151" s="22"/>
       <c r="P151" s="22"/>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152" s="22"/>
       <c r="B152" s="22"/>
       <c r="C152" s="22"/>
@@ -10206,7 +10298,7 @@
       <c r="O152" s="22"/>
       <c r="P152" s="22"/>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" s="22"/>
       <c r="B153" s="22"/>
       <c r="C153" s="22"/>
@@ -10230,7 +10322,7 @@
       <c r="O153" s="22"/>
       <c r="P153" s="22"/>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" s="22"/>
       <c r="B154" s="22"/>
       <c r="C154" s="22"/>
@@ -10254,7 +10346,7 @@
       <c r="O154" s="22"/>
       <c r="P154" s="22"/>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" s="22"/>
       <c r="B155" s="22"/>
       <c r="C155" s="22"/>
@@ -10278,7 +10370,7 @@
       <c r="O155" s="22"/>
       <c r="P155" s="22"/>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" s="22"/>
       <c r="B156" s="22"/>
       <c r="C156" s="22"/>
@@ -10302,7 +10394,7 @@
       <c r="O156" s="22"/>
       <c r="P156" s="22"/>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" s="22"/>
       <c r="B157" s="22"/>
       <c r="C157" s="22"/>
@@ -10326,7 +10418,7 @@
       <c r="O157" s="22"/>
       <c r="P157" s="22"/>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" s="22"/>
       <c r="B158" s="22"/>
       <c r="C158" s="22"/>
@@ -10350,7 +10442,7 @@
       <c r="O158" s="22"/>
       <c r="P158" s="22"/>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" s="22"/>
       <c r="B159" s="22"/>
       <c r="C159" s="22"/>
@@ -10374,7 +10466,7 @@
       <c r="O159" s="22"/>
       <c r="P159" s="22"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160" s="22"/>
       <c r="B160" s="22"/>
       <c r="C160" s="22"/>
@@ -10398,7 +10490,7 @@
       <c r="O160" s="22"/>
       <c r="P160" s="22"/>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" s="22"/>
       <c r="B161" s="22"/>
       <c r="C161" s="22"/>
@@ -10422,7 +10514,7 @@
       <c r="O161" s="22"/>
       <c r="P161" s="22"/>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" s="22"/>
       <c r="B162" s="22"/>
       <c r="C162" s="22"/>
@@ -10446,7 +10538,7 @@
       <c r="O162" s="22"/>
       <c r="P162" s="22"/>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163" s="22"/>
       <c r="B163" s="22"/>
       <c r="C163" s="22"/>
@@ -10470,7 +10562,7 @@
       <c r="O163" s="22"/>
       <c r="P163" s="22"/>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" s="22"/>
       <c r="B164" s="22"/>
       <c r="C164" s="22"/>
@@ -10494,7 +10586,7 @@
       <c r="O164" s="22"/>
       <c r="P164" s="22"/>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" s="22"/>
       <c r="B165" s="22"/>
       <c r="C165" s="22"/>
@@ -10518,7 +10610,7 @@
       <c r="O165" s="22"/>
       <c r="P165" s="22"/>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" s="22"/>
       <c r="B166" s="22"/>
       <c r="C166" s="22"/>
@@ -10542,7 +10634,7 @@
       <c r="O166" s="22"/>
       <c r="P166" s="22"/>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" s="22"/>
       <c r="B167" s="22"/>
       <c r="C167" s="22"/>
@@ -10566,7 +10658,7 @@
       <c r="O167" s="22"/>
       <c r="P167" s="22"/>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" s="22"/>
       <c r="B168" s="22"/>
       <c r="C168" s="22"/>
@@ -10590,7 +10682,7 @@
       <c r="O168" s="22"/>
       <c r="P168" s="22"/>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" s="22"/>
       <c r="B169" s="22"/>
       <c r="C169" s="22"/>
@@ -10614,7 +10706,7 @@
       <c r="O169" s="22"/>
       <c r="P169" s="22"/>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" s="22"/>
       <c r="B170" s="22"/>
       <c r="C170" s="22"/>
@@ -10638,7 +10730,7 @@
       <c r="O170" s="22"/>
       <c r="P170" s="22"/>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" s="22"/>
       <c r="B171" s="22"/>
       <c r="C171" s="22"/>
@@ -10662,7 +10754,7 @@
       <c r="O171" s="22"/>
       <c r="P171" s="22"/>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" s="22"/>
       <c r="B172" s="22"/>
       <c r="C172" s="22"/>
@@ -10686,7 +10778,7 @@
       <c r="O172" s="22"/>
       <c r="P172" s="22"/>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" s="22"/>
       <c r="B173" s="22"/>
       <c r="C173" s="22"/>
@@ -10710,7 +10802,7 @@
       <c r="O173" s="22"/>
       <c r="P173" s="22"/>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174" s="22"/>
       <c r="B174" s="22"/>
       <c r="C174" s="22"/>
@@ -10734,7 +10826,7 @@
       <c r="O174" s="22"/>
       <c r="P174" s="22"/>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175" s="22"/>
       <c r="B175" s="22"/>
       <c r="C175" s="22"/>
@@ -10758,7 +10850,7 @@
       <c r="O175" s="22"/>
       <c r="P175" s="22"/>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176" s="22"/>
       <c r="B176" s="22"/>
       <c r="C176" s="22"/>
@@ -10782,7 +10874,7 @@
       <c r="O176" s="22"/>
       <c r="P176" s="22"/>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177" s="22"/>
       <c r="B177" s="22"/>
       <c r="C177" s="22"/>
@@ -10806,7 +10898,7 @@
       <c r="O177" s="22"/>
       <c r="P177" s="22"/>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178" s="22"/>
       <c r="B178" s="22"/>
       <c r="C178" s="22"/>
@@ -10830,7 +10922,7 @@
       <c r="O178" s="22"/>
       <c r="P178" s="22"/>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179" s="22"/>
       <c r="B179" s="22"/>
       <c r="C179" s="22"/>
@@ -10854,7 +10946,7 @@
       <c r="O179" s="22"/>
       <c r="P179" s="22"/>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180" s="22"/>
       <c r="B180" s="22"/>
       <c r="C180" s="22"/>
@@ -10878,7 +10970,7 @@
       <c r="O180" s="22"/>
       <c r="P180" s="22"/>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181" s="22"/>
       <c r="B181" s="22"/>
       <c r="C181" s="22"/>
@@ -10902,7 +10994,7 @@
       <c r="O181" s="22"/>
       <c r="P181" s="22"/>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182" s="22"/>
       <c r="B182" s="22"/>
       <c r="C182" s="22"/>
@@ -10926,7 +11018,7 @@
       <c r="O182" s="22"/>
       <c r="P182" s="22"/>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183" s="22"/>
       <c r="B183" s="22"/>
       <c r="C183" s="22"/>
@@ -10950,7 +11042,7 @@
       <c r="O183" s="22"/>
       <c r="P183" s="22"/>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184" s="22"/>
       <c r="B184" s="22"/>
       <c r="C184" s="22"/>
@@ -10974,7 +11066,7 @@
       <c r="O184" s="22"/>
       <c r="P184" s="22"/>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185" s="22"/>
       <c r="B185" s="22"/>
       <c r="C185" s="22"/>
@@ -10998,7 +11090,7 @@
       <c r="O185" s="22"/>
       <c r="P185" s="22"/>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186" s="22"/>
       <c r="B186" s="22"/>
       <c r="C186" s="22"/>
@@ -11022,7 +11114,7 @@
       <c r="O186" s="22"/>
       <c r="P186" s="22"/>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187" s="22"/>
       <c r="B187" s="22"/>
       <c r="C187" s="22"/>
@@ -11046,7 +11138,7 @@
       <c r="O187" s="22"/>
       <c r="P187" s="22"/>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188" s="22"/>
       <c r="B188" s="22"/>
       <c r="C188" s="22"/>
@@ -11070,7 +11162,7 @@
       <c r="O188" s="22"/>
       <c r="P188" s="22"/>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189" s="22"/>
       <c r="B189" s="22"/>
       <c r="C189" s="22"/>
@@ -11094,7 +11186,7 @@
       <c r="O189" s="22"/>
       <c r="P189" s="22"/>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190" s="22"/>
       <c r="B190" s="22"/>
       <c r="C190" s="22"/>
@@ -11118,7 +11210,7 @@
       <c r="O190" s="22"/>
       <c r="P190" s="22"/>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191" s="22"/>
       <c r="B191" s="22"/>
       <c r="C191" s="22"/>
@@ -11142,7 +11234,7 @@
       <c r="O191" s="22"/>
       <c r="P191" s="22"/>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192" s="22"/>
       <c r="B192" s="22"/>
       <c r="C192" s="22"/>
@@ -11166,7 +11258,7 @@
       <c r="O192" s="22"/>
       <c r="P192" s="22"/>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A193" s="22"/>
       <c r="B193" s="22"/>
       <c r="C193" s="22"/>
@@ -11190,7 +11282,7 @@
       <c r="O193" s="22"/>
       <c r="P193" s="22"/>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A194" s="22"/>
       <c r="B194" s="22"/>
       <c r="C194" s="22"/>
@@ -11203,18 +11295,18 @@
       <c r="J194" s="22"/>
       <c r="K194" s="22"/>
       <c r="L194" s="23" t="str">
-        <f t="shared" ref="L194:L225" si="12">IF(COUNT(I194:K194)=3,(I194+4*J194+K194)/6,"")</f>
+        <f t="shared" ref="L194:L201" si="12">IF(COUNT(I194:K194)=3,(I194+4*J194+K194)/6,"")</f>
         <v/>
       </c>
       <c r="M194" s="22"/>
       <c r="N194" s="23" t="str">
-        <f t="shared" ref="N194:N225" si="13">IF(AND(ISNUMBER(M194),ISNUMBER(L194)),M194-L194,"")</f>
+        <f t="shared" ref="N194:N201" si="13">IF(AND(ISNUMBER(M194),ISNUMBER(L194)),M194-L194,"")</f>
         <v/>
       </c>
       <c r="O194" s="22"/>
       <c r="P194" s="22"/>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A195" s="22"/>
       <c r="B195" s="22"/>
       <c r="C195" s="22"/>
@@ -11238,7 +11330,7 @@
       <c r="O195" s="22"/>
       <c r="P195" s="22"/>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A196" s="22"/>
       <c r="B196" s="22"/>
       <c r="C196" s="22"/>
@@ -11262,7 +11354,7 @@
       <c r="O196" s="22"/>
       <c r="P196" s="22"/>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A197" s="22"/>
       <c r="B197" s="22"/>
       <c r="C197" s="22"/>
@@ -11286,7 +11378,7 @@
       <c r="O197" s="22"/>
       <c r="P197" s="22"/>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A198" s="22"/>
       <c r="B198" s="22"/>
       <c r="C198" s="22"/>
@@ -11310,7 +11402,7 @@
       <c r="O198" s="22"/>
       <c r="P198" s="22"/>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A199" s="22"/>
       <c r="B199" s="22"/>
       <c r="C199" s="22"/>
@@ -11334,7 +11426,7 @@
       <c r="O199" s="22"/>
       <c r="P199" s="22"/>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A200" s="22"/>
       <c r="B200" s="22"/>
       <c r="C200" s="22"/>
@@ -11358,7 +11450,7 @@
       <c r="O200" s="22"/>
       <c r="P200" s="22"/>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A201" s="22"/>
       <c r="B201" s="22"/>
       <c r="C201" s="22"/>
@@ -11405,7 +11497,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -11419,7 +11511,7 @@
     <col min="11" max="11" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>79</v>
       </c>
@@ -11454,7 +11546,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -11486,7 +11578,7 @@
       <c r="J2" s="22"/>
       <c r="K2" s="22"/>
     </row>
-    <row r="3" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A3" s="22">
         <v>2</v>
       </c>
@@ -11518,7 +11610,7 @@
       <c r="J3" s="22"/>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="25" x14ac:dyDescent="0.35">
       <c r="A4" s="22">
         <v>3</v>
       </c>
@@ -11550,7 +11642,7 @@
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>107</v>
       </c>
@@ -11570,14 +11662,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
     <col min="6" max="8" width="10" customWidth="1"/>
     <col min="11" max="13" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>108</v>
       </c>
@@ -11588,7 +11680,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="28" t="s">
         <v>111</v>
       </c>
@@ -11611,7 +11703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="30" t="s">
         <v>112</v>
       </c>
@@ -11640,7 +11732,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="31">
         <v>0</v>
       </c>
@@ -11666,7 +11758,7 @@
       </c>
       <c r="M5" s="33"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="31">
         <v>1</v>
       </c>
@@ -11692,7 +11784,7 @@
       </c>
       <c r="M6" s="33"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="31">
         <v>2</v>
       </c>
@@ -11718,7 +11810,7 @@
       </c>
       <c r="M7" s="33"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="31">
         <v>3</v>
       </c>
@@ -11744,7 +11836,7 @@
       </c>
       <c r="M8" s="33"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="31">
         <v>4</v>
       </c>
@@ -11770,7 +11862,7 @@
       </c>
       <c r="M9" s="33"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="31">
         <v>5</v>
       </c>
@@ -11796,7 +11888,7 @@
       </c>
       <c r="M10" s="33"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="31">
         <v>6</v>
       </c>
@@ -11822,7 +11914,7 @@
       </c>
       <c r="M11" s="33"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="31">
         <v>7</v>
       </c>
@@ -11848,7 +11940,7 @@
       </c>
       <c r="M12" s="33"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="31">
         <v>8</v>
       </c>
@@ -11874,7 +11966,7 @@
       </c>
       <c r="M13" s="33"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="31">
         <v>9</v>
       </c>
@@ -11900,7 +11992,7 @@
       </c>
       <c r="M14" s="33"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="31">
         <v>10</v>
       </c>
@@ -11926,7 +12018,7 @@
       </c>
       <c r="M15" s="33"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="31">
         <v>11</v>
       </c>
@@ -11952,7 +12044,7 @@
       </c>
       <c r="M16" s="33"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="31">
         <v>12</v>
       </c>
@@ -11978,7 +12070,7 @@
       </c>
       <c r="M17" s="33"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="31">
         <v>13</v>
       </c>
@@ -12004,7 +12096,7 @@
       </c>
       <c r="M18" s="33"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="31">
         <v>14</v>
       </c>
@@ -12030,7 +12122,7 @@
       </c>
       <c r="M19" s="33"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>115</v>
       </c>
@@ -12045,7 +12137,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -12060,7 +12152,7 @@
     <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>72</v>
       </c>
@@ -12098,7 +12190,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="26" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>88</v>
       </c>
@@ -12136,7 +12228,7 @@
       </c>
       <c r="L2" s="19"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -12156,7 +12248,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="22"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="22"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -12176,7 +12268,7 @@
       <c r="K4" s="22"/>
       <c r="L4" s="22"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="22"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
@@ -12196,7 +12288,7 @@
       <c r="K5" s="22"/>
       <c r="L5" s="22"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="22"/>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
@@ -12216,7 +12308,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="22"/>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -12236,7 +12328,7 @@
       <c r="K7" s="22"/>
       <c r="L7" s="22"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="22"/>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -12256,7 +12348,7 @@
       <c r="K8" s="22"/>
       <c r="L8" s="22"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="22"/>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -12276,7 +12368,7 @@
       <c r="K9" s="22"/>
       <c r="L9" s="22"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
@@ -12296,7 +12388,7 @@
       <c r="K10" s="22"/>
       <c r="L10" s="22"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="22"/>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -12316,7 +12408,7 @@
       <c r="K11" s="22"/>
       <c r="L11" s="22"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="22"/>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -12336,7 +12428,7 @@
       <c r="K12" s="22"/>
       <c r="L12" s="22"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="22"/>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
@@ -12356,7 +12448,7 @@
       <c r="K13" s="22"/>
       <c r="L13" s="22"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="22"/>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -12376,7 +12468,7 @@
       <c r="K14" s="22"/>
       <c r="L14" s="22"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="22"/>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -12396,7 +12488,7 @@
       <c r="K15" s="22"/>
       <c r="L15" s="22"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -12416,7 +12508,7 @@
       <c r="K16" s="22"/>
       <c r="L16" s="22"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="22"/>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -12436,7 +12528,7 @@
       <c r="K17" s="22"/>
       <c r="L17" s="22"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="22"/>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -12456,7 +12548,7 @@
       <c r="K18" s="22"/>
       <c r="L18" s="22"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="22"/>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -12476,7 +12568,7 @@
       <c r="K19" s="22"/>
       <c r="L19" s="22"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -12496,7 +12588,7 @@
       <c r="K20" s="22"/>
       <c r="L20" s="22"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
@@ -12516,7 +12608,7 @@
       <c r="K21" s="22"/>
       <c r="L21" s="22"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="22"/>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -12536,7 +12628,7 @@
       <c r="K22" s="22"/>
       <c r="L22" s="22"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -12556,7 +12648,7 @@
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -12576,7 +12668,7 @@
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -12596,7 +12688,7 @@
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -12616,7 +12708,7 @@
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="22"/>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -12636,7 +12728,7 @@
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -12656,7 +12748,7 @@
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -12676,7 +12768,7 @@
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
@@ -12696,7 +12788,7 @@
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -12716,7 +12808,7 @@
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
@@ -12736,7 +12828,7 @@
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
@@ -12756,18 +12848,18 @@
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
       <c r="F34" s="34" t="str">
-        <f t="shared" ref="F34:F65" si="2">IF(AND(ISNUMBER(D34),ISNUMBER(E34)),D34*E34,"")</f>
+        <f t="shared" ref="F34:F61" si="2">IF(AND(ISNUMBER(D34),ISNUMBER(E34)),D34*E34,"")</f>
         <v/>
       </c>
       <c r="G34" s="34" t="str">
-        <f t="shared" ref="G34:G65" si="3">IF(F34="","",IF(F34&gt;=15,"hoch",IF(F34&gt;=8,"mittel","niedrig")))</f>
+        <f t="shared" ref="G34:G61" si="3">IF(F34="","",IF(F34&gt;=15,"hoch",IF(F34&gt;=8,"mittel","niedrig")))</f>
         <v/>
       </c>
       <c r="H34" s="22"/>
@@ -12776,7 +12868,7 @@
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="22"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
@@ -12796,7 +12888,7 @@
       <c r="K35" s="22"/>
       <c r="L35" s="22"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="22"/>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -12816,7 +12908,7 @@
       <c r="K36" s="22"/>
       <c r="L36" s="22"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="22"/>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
@@ -12836,7 +12928,7 @@
       <c r="K37" s="22"/>
       <c r="L37" s="22"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="22"/>
       <c r="B38" s="22"/>
       <c r="C38" s="22"/>
@@ -12856,7 +12948,7 @@
       <c r="K38" s="22"/>
       <c r="L38" s="22"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="22"/>
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
@@ -12876,7 +12968,7 @@
       <c r="K39" s="22"/>
       <c r="L39" s="22"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="22"/>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -12896,7 +12988,7 @@
       <c r="K40" s="22"/>
       <c r="L40" s="22"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="22"/>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -12916,7 +13008,7 @@
       <c r="K41" s="22"/>
       <c r="L41" s="22"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="22"/>
       <c r="B42" s="22"/>
       <c r="C42" s="22"/>
@@ -12936,7 +13028,7 @@
       <c r="K42" s="22"/>
       <c r="L42" s="22"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="22"/>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
@@ -12956,7 +13048,7 @@
       <c r="K43" s="22"/>
       <c r="L43" s="22"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="22"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -12976,7 +13068,7 @@
       <c r="K44" s="22"/>
       <c r="L44" s="22"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="22"/>
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
@@ -12996,7 +13088,7 @@
       <c r="K45" s="22"/>
       <c r="L45" s="22"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="22"/>
       <c r="B46" s="22"/>
       <c r="C46" s="22"/>
@@ -13016,7 +13108,7 @@
       <c r="K46" s="22"/>
       <c r="L46" s="22"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="22"/>
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
@@ -13036,7 +13128,7 @@
       <c r="K47" s="22"/>
       <c r="L47" s="22"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="22"/>
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
@@ -13056,7 +13148,7 @@
       <c r="K48" s="22"/>
       <c r="L48" s="22"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="22"/>
       <c r="B49" s="22"/>
       <c r="C49" s="22"/>
@@ -13076,7 +13168,7 @@
       <c r="K49" s="22"/>
       <c r="L49" s="22"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="22"/>
       <c r="B50" s="22"/>
       <c r="C50" s="22"/>
@@ -13096,7 +13188,7 @@
       <c r="K50" s="22"/>
       <c r="L50" s="22"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="22"/>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
@@ -13116,7 +13208,7 @@
       <c r="K51" s="22"/>
       <c r="L51" s="22"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="22"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -13136,7 +13228,7 @@
       <c r="K52" s="22"/>
       <c r="L52" s="22"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="22"/>
       <c r="B53" s="22"/>
       <c r="C53" s="22"/>
@@ -13156,7 +13248,7 @@
       <c r="K53" s="22"/>
       <c r="L53" s="22"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="22"/>
       <c r="B54" s="22"/>
       <c r="C54" s="22"/>
@@ -13176,7 +13268,7 @@
       <c r="K54" s="22"/>
       <c r="L54" s="22"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="22"/>
       <c r="B55" s="22"/>
       <c r="C55" s="22"/>
@@ -13196,7 +13288,7 @@
       <c r="K55" s="22"/>
       <c r="L55" s="22"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="22"/>
       <c r="B56" s="22"/>
       <c r="C56" s="22"/>
@@ -13216,7 +13308,7 @@
       <c r="K56" s="22"/>
       <c r="L56" s="22"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="22"/>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
@@ -13236,7 +13328,7 @@
       <c r="K57" s="22"/>
       <c r="L57" s="22"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="22"/>
       <c r="B58" s="22"/>
       <c r="C58" s="22"/>
@@ -13256,7 +13348,7 @@
       <c r="K58" s="22"/>
       <c r="L58" s="22"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="22"/>
       <c r="B59" s="22"/>
       <c r="C59" s="22"/>
@@ -13276,7 +13368,7 @@
       <c r="K59" s="22"/>
       <c r="L59" s="22"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="22"/>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -13296,7 +13388,7 @@
       <c r="K60" s="22"/>
       <c r="L60" s="22"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="22"/>
       <c r="B61" s="22"/>
       <c r="C61" s="22"/>
@@ -13360,7 +13452,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:M201"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -13374,7 +13466,7 @@
     <col min="13" max="13" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>72</v>
       </c>
@@ -13415,7 +13507,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="26" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>88</v>
       </c>
@@ -13454,7 +13546,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -13469,7 +13561,7 @@
       <c r="L3" s="20"/>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="22"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -13484,7 +13576,7 @@
       <c r="L4" s="20"/>
       <c r="M4" s="22"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="22"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
@@ -13499,7 +13591,7 @@
       <c r="L5" s="20"/>
       <c r="M5" s="22"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="22"/>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
@@ -13514,7 +13606,7 @@
       <c r="L6" s="20"/>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="22"/>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -13529,7 +13621,7 @@
       <c r="L7" s="20"/>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="22"/>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -13544,7 +13636,7 @@
       <c r="L8" s="20"/>
       <c r="M8" s="22"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="22"/>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -13559,7 +13651,7 @@
       <c r="L9" s="20"/>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
@@ -13574,7 +13666,7 @@
       <c r="L10" s="20"/>
       <c r="M10" s="22"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="22"/>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -13589,7 +13681,7 @@
       <c r="L11" s="20"/>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="22"/>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -13604,7 +13696,7 @@
       <c r="L12" s="20"/>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="22"/>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
@@ -13619,7 +13711,7 @@
       <c r="L13" s="20"/>
       <c r="M13" s="22"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="22"/>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -13634,7 +13726,7 @@
       <c r="L14" s="20"/>
       <c r="M14" s="22"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="22"/>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -13649,7 +13741,7 @@
       <c r="L15" s="20"/>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -13664,7 +13756,7 @@
       <c r="L16" s="20"/>
       <c r="M16" s="22"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="22"/>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -13679,7 +13771,7 @@
       <c r="L17" s="20"/>
       <c r="M17" s="22"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="22"/>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -13694,7 +13786,7 @@
       <c r="L18" s="20"/>
       <c r="M18" s="22"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="22"/>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -13709,7 +13801,7 @@
       <c r="L19" s="20"/>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -13724,7 +13816,7 @@
       <c r="L20" s="20"/>
       <c r="M20" s="22"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
@@ -13739,7 +13831,7 @@
       <c r="L21" s="20"/>
       <c r="M21" s="22"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="22"/>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -13754,7 +13846,7 @@
       <c r="L22" s="20"/>
       <c r="M22" s="22"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -13769,7 +13861,7 @@
       <c r="L23" s="20"/>
       <c r="M23" s="22"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -13784,7 +13876,7 @@
       <c r="L24" s="20"/>
       <c r="M24" s="22"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -13799,7 +13891,7 @@
       <c r="L25" s="20"/>
       <c r="M25" s="22"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -13814,7 +13906,7 @@
       <c r="L26" s="20"/>
       <c r="M26" s="22"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="22"/>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -13829,7 +13921,7 @@
       <c r="L27" s="20"/>
       <c r="M27" s="22"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -13844,7 +13936,7 @@
       <c r="L28" s="20"/>
       <c r="M28" s="22"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -13859,7 +13951,7 @@
       <c r="L29" s="20"/>
       <c r="M29" s="22"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
@@ -13874,7 +13966,7 @@
       <c r="L30" s="20"/>
       <c r="M30" s="22"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -13889,7 +13981,7 @@
       <c r="L31" s="20"/>
       <c r="M31" s="22"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
@@ -13904,7 +13996,7 @@
       <c r="L32" s="20"/>
       <c r="M32" s="22"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
@@ -13919,7 +14011,7 @@
       <c r="L33" s="20"/>
       <c r="M33" s="22"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
@@ -13934,7 +14026,7 @@
       <c r="L34" s="20"/>
       <c r="M34" s="22"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="22"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
@@ -13949,7 +14041,7 @@
       <c r="L35" s="20"/>
       <c r="M35" s="22"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="22"/>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -13964,7 +14056,7 @@
       <c r="L36" s="20"/>
       <c r="M36" s="22"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="22"/>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
@@ -13979,7 +14071,7 @@
       <c r="L37" s="20"/>
       <c r="M37" s="22"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="22"/>
       <c r="B38" s="22"/>
       <c r="C38" s="22"/>
@@ -13994,7 +14086,7 @@
       <c r="L38" s="20"/>
       <c r="M38" s="22"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="22"/>
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
@@ -14009,7 +14101,7 @@
       <c r="L39" s="20"/>
       <c r="M39" s="22"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="22"/>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -14024,7 +14116,7 @@
       <c r="L40" s="20"/>
       <c r="M40" s="22"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="22"/>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -14039,7 +14131,7 @@
       <c r="L41" s="20"/>
       <c r="M41" s="22"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="22"/>
       <c r="B42" s="22"/>
       <c r="C42" s="22"/>
@@ -14054,7 +14146,7 @@
       <c r="L42" s="20"/>
       <c r="M42" s="22"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="22"/>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
@@ -14069,7 +14161,7 @@
       <c r="L43" s="20"/>
       <c r="M43" s="22"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="22"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -14084,7 +14176,7 @@
       <c r="L44" s="20"/>
       <c r="M44" s="22"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="22"/>
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
@@ -14099,7 +14191,7 @@
       <c r="L45" s="20"/>
       <c r="M45" s="22"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="22"/>
       <c r="B46" s="22"/>
       <c r="C46" s="22"/>
@@ -14114,7 +14206,7 @@
       <c r="L46" s="20"/>
       <c r="M46" s="22"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="22"/>
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
@@ -14129,7 +14221,7 @@
       <c r="L47" s="20"/>
       <c r="M47" s="22"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="22"/>
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
@@ -14144,7 +14236,7 @@
       <c r="L48" s="20"/>
       <c r="M48" s="22"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="22"/>
       <c r="B49" s="22"/>
       <c r="C49" s="22"/>
@@ -14159,7 +14251,7 @@
       <c r="L49" s="20"/>
       <c r="M49" s="22"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="22"/>
       <c r="B50" s="22"/>
       <c r="C50" s="22"/>
@@ -14174,7 +14266,7 @@
       <c r="L50" s="20"/>
       <c r="M50" s="22"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="22"/>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
@@ -14189,7 +14281,7 @@
       <c r="L51" s="20"/>
       <c r="M51" s="22"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="22"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -14204,7 +14296,7 @@
       <c r="L52" s="20"/>
       <c r="M52" s="22"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="22"/>
       <c r="B53" s="22"/>
       <c r="C53" s="22"/>
@@ -14219,7 +14311,7 @@
       <c r="L53" s="20"/>
       <c r="M53" s="22"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="22"/>
       <c r="B54" s="22"/>
       <c r="C54" s="22"/>
@@ -14234,7 +14326,7 @@
       <c r="L54" s="20"/>
       <c r="M54" s="22"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="22"/>
       <c r="B55" s="22"/>
       <c r="C55" s="22"/>
@@ -14249,7 +14341,7 @@
       <c r="L55" s="20"/>
       <c r="M55" s="22"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="22"/>
       <c r="B56" s="22"/>
       <c r="C56" s="22"/>
@@ -14264,7 +14356,7 @@
       <c r="L56" s="20"/>
       <c r="M56" s="22"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="22"/>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
@@ -14279,7 +14371,7 @@
       <c r="L57" s="20"/>
       <c r="M57" s="22"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="22"/>
       <c r="B58" s="22"/>
       <c r="C58" s="22"/>
@@ -14294,7 +14386,7 @@
       <c r="L58" s="20"/>
       <c r="M58" s="22"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="22"/>
       <c r="B59" s="22"/>
       <c r="C59" s="22"/>
@@ -14309,7 +14401,7 @@
       <c r="L59" s="20"/>
       <c r="M59" s="22"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="22"/>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -14324,7 +14416,7 @@
       <c r="L60" s="20"/>
       <c r="M60" s="22"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="22"/>
       <c r="B61" s="22"/>
       <c r="C61" s="22"/>
@@ -14339,7 +14431,7 @@
       <c r="L61" s="20"/>
       <c r="M61" s="22"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="22"/>
       <c r="B62" s="22"/>
       <c r="C62" s="22"/>
@@ -14354,7 +14446,7 @@
       <c r="L62" s="20"/>
       <c r="M62" s="22"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="22"/>
       <c r="B63" s="22"/>
       <c r="C63" s="22"/>
@@ -14369,7 +14461,7 @@
       <c r="L63" s="20"/>
       <c r="M63" s="22"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="22"/>
       <c r="B64" s="22"/>
       <c r="C64" s="22"/>
@@ -14384,7 +14476,7 @@
       <c r="L64" s="20"/>
       <c r="M64" s="22"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="22"/>
       <c r="B65" s="22"/>
       <c r="C65" s="22"/>
@@ -14399,7 +14491,7 @@
       <c r="L65" s="20"/>
       <c r="M65" s="22"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="22"/>
       <c r="B66" s="22"/>
       <c r="C66" s="22"/>
@@ -14414,7 +14506,7 @@
       <c r="L66" s="20"/>
       <c r="M66" s="22"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="22"/>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -14429,7 +14521,7 @@
       <c r="L67" s="20"/>
       <c r="M67" s="22"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="22"/>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -14444,7 +14536,7 @@
       <c r="L68" s="20"/>
       <c r="M68" s="22"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="22"/>
       <c r="B69" s="22"/>
       <c r="C69" s="22"/>
@@ -14459,7 +14551,7 @@
       <c r="L69" s="20"/>
       <c r="M69" s="22"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" s="22"/>
       <c r="B70" s="22"/>
       <c r="C70" s="22"/>
@@ -14474,7 +14566,7 @@
       <c r="L70" s="20"/>
       <c r="M70" s="22"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" s="22"/>
       <c r="B71" s="22"/>
       <c r="C71" s="22"/>
@@ -14489,7 +14581,7 @@
       <c r="L71" s="20"/>
       <c r="M71" s="22"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" s="22"/>
       <c r="B72" s="22"/>
       <c r="C72" s="22"/>
@@ -14504,7 +14596,7 @@
       <c r="L72" s="20"/>
       <c r="M72" s="22"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" s="22"/>
       <c r="B73" s="22"/>
       <c r="C73" s="22"/>
@@ -14519,7 +14611,7 @@
       <c r="L73" s="20"/>
       <c r="M73" s="22"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" s="22"/>
       <c r="B74" s="22"/>
       <c r="C74" s="22"/>
@@ -14534,7 +14626,7 @@
       <c r="L74" s="20"/>
       <c r="M74" s="22"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" s="22"/>
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
@@ -14549,7 +14641,7 @@
       <c r="L75" s="20"/>
       <c r="M75" s="22"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" s="22"/>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -14564,7 +14656,7 @@
       <c r="L76" s="20"/>
       <c r="M76" s="22"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" s="22"/>
       <c r="B77" s="22"/>
       <c r="C77" s="22"/>
@@ -14579,7 +14671,7 @@
       <c r="L77" s="20"/>
       <c r="M77" s="22"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" s="22"/>
       <c r="B78" s="22"/>
       <c r="C78" s="22"/>
@@ -14594,7 +14686,7 @@
       <c r="L78" s="20"/>
       <c r="M78" s="22"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" s="22"/>
       <c r="B79" s="22"/>
       <c r="C79" s="22"/>
@@ -14609,7 +14701,7 @@
       <c r="L79" s="20"/>
       <c r="M79" s="22"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" s="22"/>
       <c r="B80" s="22"/>
       <c r="C80" s="22"/>
@@ -14624,7 +14716,7 @@
       <c r="L80" s="20"/>
       <c r="M80" s="22"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="22"/>
       <c r="B81" s="22"/>
       <c r="C81" s="22"/>
@@ -14639,7 +14731,7 @@
       <c r="L81" s="20"/>
       <c r="M81" s="22"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="22"/>
       <c r="B82" s="22"/>
       <c r="C82" s="22"/>
@@ -14654,7 +14746,7 @@
       <c r="L82" s="20"/>
       <c r="M82" s="22"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="22"/>
       <c r="B83" s="22"/>
       <c r="C83" s="22"/>
@@ -14669,7 +14761,7 @@
       <c r="L83" s="20"/>
       <c r="M83" s="22"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="22"/>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -14684,7 +14776,7 @@
       <c r="L84" s="20"/>
       <c r="M84" s="22"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="22"/>
       <c r="B85" s="22"/>
       <c r="C85" s="22"/>
@@ -14699,7 +14791,7 @@
       <c r="L85" s="20"/>
       <c r="M85" s="22"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="22"/>
       <c r="B86" s="22"/>
       <c r="C86" s="22"/>
@@ -14714,7 +14806,7 @@
       <c r="L86" s="20"/>
       <c r="M86" s="22"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" s="22"/>
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
@@ -14729,7 +14821,7 @@
       <c r="L87" s="20"/>
       <c r="M87" s="22"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" s="22"/>
       <c r="B88" s="22"/>
       <c r="C88" s="22"/>
@@ -14744,7 +14836,7 @@
       <c r="L88" s="20"/>
       <c r="M88" s="22"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" s="22"/>
       <c r="B89" s="22"/>
       <c r="C89" s="22"/>
@@ -14759,7 +14851,7 @@
       <c r="L89" s="20"/>
       <c r="M89" s="22"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" s="22"/>
       <c r="B90" s="22"/>
       <c r="C90" s="22"/>
@@ -14774,7 +14866,7 @@
       <c r="L90" s="20"/>
       <c r="M90" s="22"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="22"/>
       <c r="B91" s="22"/>
       <c r="C91" s="22"/>
@@ -14789,7 +14881,7 @@
       <c r="L91" s="20"/>
       <c r="M91" s="22"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="22"/>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -14804,7 +14896,7 @@
       <c r="L92" s="20"/>
       <c r="M92" s="22"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" s="22"/>
       <c r="B93" s="22"/>
       <c r="C93" s="22"/>
@@ -14819,7 +14911,7 @@
       <c r="L93" s="20"/>
       <c r="M93" s="22"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" s="22"/>
       <c r="B94" s="22"/>
       <c r="C94" s="22"/>
@@ -14834,7 +14926,7 @@
       <c r="L94" s="20"/>
       <c r="M94" s="22"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" s="22"/>
       <c r="B95" s="22"/>
       <c r="C95" s="22"/>
@@ -14849,7 +14941,7 @@
       <c r="L95" s="20"/>
       <c r="M95" s="22"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" s="22"/>
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
@@ -14864,7 +14956,7 @@
       <c r="L96" s="20"/>
       <c r="M96" s="22"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="22"/>
       <c r="B97" s="22"/>
       <c r="C97" s="22"/>
@@ -14879,7 +14971,7 @@
       <c r="L97" s="20"/>
       <c r="M97" s="22"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="22"/>
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
@@ -14894,7 +14986,7 @@
       <c r="L98" s="20"/>
       <c r="M98" s="22"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="22"/>
       <c r="B99" s="22"/>
       <c r="C99" s="22"/>
@@ -14909,7 +15001,7 @@
       <c r="L99" s="20"/>
       <c r="M99" s="22"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" s="22"/>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -14924,7 +15016,7 @@
       <c r="L100" s="20"/>
       <c r="M100" s="22"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" s="22"/>
       <c r="B101" s="22"/>
       <c r="C101" s="22"/>
@@ -14939,7 +15031,7 @@
       <c r="L101" s="20"/>
       <c r="M101" s="22"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" s="22"/>
       <c r="B102" s="22"/>
       <c r="C102" s="22"/>
@@ -14954,7 +15046,7 @@
       <c r="L102" s="20"/>
       <c r="M102" s="22"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" s="22"/>
       <c r="B103" s="22"/>
       <c r="C103" s="22"/>
@@ -14969,7 +15061,7 @@
       <c r="L103" s="20"/>
       <c r="M103" s="22"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" s="22"/>
       <c r="B104" s="22"/>
       <c r="C104" s="22"/>
@@ -14984,7 +15076,7 @@
       <c r="L104" s="20"/>
       <c r="M104" s="22"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" s="22"/>
       <c r="B105" s="22"/>
       <c r="C105" s="22"/>
@@ -14999,7 +15091,7 @@
       <c r="L105" s="20"/>
       <c r="M105" s="22"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" s="22"/>
       <c r="B106" s="22"/>
       <c r="C106" s="22"/>
@@ -15014,7 +15106,7 @@
       <c r="L106" s="20"/>
       <c r="M106" s="22"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" s="22"/>
       <c r="B107" s="22"/>
       <c r="C107" s="22"/>
@@ -15029,7 +15121,7 @@
       <c r="L107" s="20"/>
       <c r="M107" s="22"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="22"/>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
@@ -15044,7 +15136,7 @@
       <c r="L108" s="20"/>
       <c r="M108" s="22"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="22"/>
       <c r="B109" s="22"/>
       <c r="C109" s="22"/>
@@ -15059,7 +15151,7 @@
       <c r="L109" s="20"/>
       <c r="M109" s="22"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="22"/>
       <c r="B110" s="22"/>
       <c r="C110" s="22"/>
@@ -15074,7 +15166,7 @@
       <c r="L110" s="20"/>
       <c r="M110" s="22"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="22"/>
       <c r="B111" s="22"/>
       <c r="C111" s="22"/>
@@ -15089,7 +15181,7 @@
       <c r="L111" s="20"/>
       <c r="M111" s="22"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" s="22"/>
       <c r="B112" s="22"/>
       <c r="C112" s="22"/>
@@ -15104,7 +15196,7 @@
       <c r="L112" s="20"/>
       <c r="M112" s="22"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" s="22"/>
       <c r="B113" s="22"/>
       <c r="C113" s="22"/>
@@ -15119,7 +15211,7 @@
       <c r="L113" s="20"/>
       <c r="M113" s="22"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" s="22"/>
       <c r="B114" s="22"/>
       <c r="C114" s="22"/>
@@ -15134,7 +15226,7 @@
       <c r="L114" s="20"/>
       <c r="M114" s="22"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" s="22"/>
       <c r="B115" s="22"/>
       <c r="C115" s="22"/>
@@ -15149,7 +15241,7 @@
       <c r="L115" s="20"/>
       <c r="M115" s="22"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" s="22"/>
       <c r="B116" s="22"/>
       <c r="C116" s="22"/>
@@ -15164,7 +15256,7 @@
       <c r="L116" s="20"/>
       <c r="M116" s="22"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" s="22"/>
       <c r="B117" s="22"/>
       <c r="C117" s="22"/>
@@ -15179,7 +15271,7 @@
       <c r="L117" s="20"/>
       <c r="M117" s="22"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" s="22"/>
       <c r="B118" s="22"/>
       <c r="C118" s="22"/>
@@ -15194,7 +15286,7 @@
       <c r="L118" s="20"/>
       <c r="M118" s="22"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" s="22"/>
       <c r="B119" s="22"/>
       <c r="C119" s="22"/>
@@ -15209,7 +15301,7 @@
       <c r="L119" s="20"/>
       <c r="M119" s="22"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" s="22"/>
       <c r="B120" s="22"/>
       <c r="C120" s="22"/>
@@ -15224,7 +15316,7 @@
       <c r="L120" s="20"/>
       <c r="M120" s="22"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" s="22"/>
       <c r="B121" s="22"/>
       <c r="C121" s="22"/>
@@ -15239,7 +15331,7 @@
       <c r="L121" s="20"/>
       <c r="M121" s="22"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" s="22"/>
       <c r="B122" s="22"/>
       <c r="C122" s="22"/>
@@ -15254,7 +15346,7 @@
       <c r="L122" s="20"/>
       <c r="M122" s="22"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" s="22"/>
       <c r="B123" s="22"/>
       <c r="C123" s="22"/>
@@ -15269,7 +15361,7 @@
       <c r="L123" s="20"/>
       <c r="M123" s="22"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" s="22"/>
       <c r="B124" s="22"/>
       <c r="C124" s="22"/>
@@ -15284,7 +15376,7 @@
       <c r="L124" s="20"/>
       <c r="M124" s="22"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" s="22"/>
       <c r="B125" s="22"/>
       <c r="C125" s="22"/>
@@ -15299,7 +15391,7 @@
       <c r="L125" s="20"/>
       <c r="M125" s="22"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" s="22"/>
       <c r="B126" s="22"/>
       <c r="C126" s="22"/>
@@ -15314,7 +15406,7 @@
       <c r="L126" s="20"/>
       <c r="M126" s="22"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" s="22"/>
       <c r="B127" s="22"/>
       <c r="C127" s="22"/>
@@ -15329,7 +15421,7 @@
       <c r="L127" s="20"/>
       <c r="M127" s="22"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" s="22"/>
       <c r="B128" s="22"/>
       <c r="C128" s="22"/>
@@ -15344,7 +15436,7 @@
       <c r="L128" s="20"/>
       <c r="M128" s="22"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" s="22"/>
       <c r="B129" s="22"/>
       <c r="C129" s="22"/>
@@ -15359,7 +15451,7 @@
       <c r="L129" s="20"/>
       <c r="M129" s="22"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" s="22"/>
       <c r="B130" s="22"/>
       <c r="C130" s="22"/>
@@ -15374,7 +15466,7 @@
       <c r="L130" s="20"/>
       <c r="M130" s="22"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" s="22"/>
       <c r="B131" s="22"/>
       <c r="C131" s="22"/>
@@ -15389,7 +15481,7 @@
       <c r="L131" s="20"/>
       <c r="M131" s="22"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" s="22"/>
       <c r="B132" s="22"/>
       <c r="C132" s="22"/>
@@ -15404,7 +15496,7 @@
       <c r="L132" s="20"/>
       <c r="M132" s="22"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" s="22"/>
       <c r="B133" s="22"/>
       <c r="C133" s="22"/>
@@ -15419,7 +15511,7 @@
       <c r="L133" s="20"/>
       <c r="M133" s="22"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" s="22"/>
       <c r="B134" s="22"/>
       <c r="C134" s="22"/>
@@ -15434,7 +15526,7 @@
       <c r="L134" s="20"/>
       <c r="M134" s="22"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="22"/>
       <c r="B135" s="22"/>
       <c r="C135" s="22"/>
@@ -15449,7 +15541,7 @@
       <c r="L135" s="20"/>
       <c r="M135" s="22"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="22"/>
       <c r="B136" s="22"/>
       <c r="C136" s="22"/>
@@ -15464,7 +15556,7 @@
       <c r="L136" s="20"/>
       <c r="M136" s="22"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="22"/>
       <c r="B137" s="22"/>
       <c r="C137" s="22"/>
@@ -15479,7 +15571,7 @@
       <c r="L137" s="20"/>
       <c r="M137" s="22"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="22"/>
       <c r="B138" s="22"/>
       <c r="C138" s="22"/>
@@ -15494,7 +15586,7 @@
       <c r="L138" s="20"/>
       <c r="M138" s="22"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" s="22"/>
       <c r="B139" s="22"/>
       <c r="C139" s="22"/>
@@ -15509,7 +15601,7 @@
       <c r="L139" s="20"/>
       <c r="M139" s="22"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" s="22"/>
       <c r="B140" s="22"/>
       <c r="C140" s="22"/>
@@ -15524,7 +15616,7 @@
       <c r="L140" s="20"/>
       <c r="M140" s="22"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" s="22"/>
       <c r="B141" s="22"/>
       <c r="C141" s="22"/>
@@ -15539,7 +15631,7 @@
       <c r="L141" s="20"/>
       <c r="M141" s="22"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" s="22"/>
       <c r="B142" s="22"/>
       <c r="C142" s="22"/>
@@ -15554,7 +15646,7 @@
       <c r="L142" s="20"/>
       <c r="M142" s="22"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" s="22"/>
       <c r="B143" s="22"/>
       <c r="C143" s="22"/>
@@ -15569,7 +15661,7 @@
       <c r="L143" s="20"/>
       <c r="M143" s="22"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" s="22"/>
       <c r="B144" s="22"/>
       <c r="C144" s="22"/>
@@ -15584,7 +15676,7 @@
       <c r="L144" s="20"/>
       <c r="M144" s="22"/>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A145" s="22"/>
       <c r="B145" s="22"/>
       <c r="C145" s="22"/>
@@ -15599,7 +15691,7 @@
       <c r="L145" s="20"/>
       <c r="M145" s="22"/>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A146" s="22"/>
       <c r="B146" s="22"/>
       <c r="C146" s="22"/>
@@ -15614,7 +15706,7 @@
       <c r="L146" s="20"/>
       <c r="M146" s="22"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A147" s="22"/>
       <c r="B147" s="22"/>
       <c r="C147" s="22"/>
@@ -15629,7 +15721,7 @@
       <c r="L147" s="20"/>
       <c r="M147" s="22"/>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A148" s="22"/>
       <c r="B148" s="22"/>
       <c r="C148" s="22"/>
@@ -15644,7 +15736,7 @@
       <c r="L148" s="20"/>
       <c r="M148" s="22"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A149" s="22"/>
       <c r="B149" s="22"/>
       <c r="C149" s="22"/>
@@ -15659,7 +15751,7 @@
       <c r="L149" s="20"/>
       <c r="M149" s="22"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A150" s="22"/>
       <c r="B150" s="22"/>
       <c r="C150" s="22"/>
@@ -15674,7 +15766,7 @@
       <c r="L150" s="20"/>
       <c r="M150" s="22"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A151" s="22"/>
       <c r="B151" s="22"/>
       <c r="C151" s="22"/>
@@ -15689,7 +15781,7 @@
       <c r="L151" s="20"/>
       <c r="M151" s="22"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A152" s="22"/>
       <c r="B152" s="22"/>
       <c r="C152" s="22"/>
@@ -15704,7 +15796,7 @@
       <c r="L152" s="20"/>
       <c r="M152" s="22"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A153" s="22"/>
       <c r="B153" s="22"/>
       <c r="C153" s="22"/>
@@ -15719,7 +15811,7 @@
       <c r="L153" s="20"/>
       <c r="M153" s="22"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A154" s="22"/>
       <c r="B154" s="22"/>
       <c r="C154" s="22"/>
@@ -15734,7 +15826,7 @@
       <c r="L154" s="20"/>
       <c r="M154" s="22"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A155" s="22"/>
       <c r="B155" s="22"/>
       <c r="C155" s="22"/>
@@ -15749,7 +15841,7 @@
       <c r="L155" s="20"/>
       <c r="M155" s="22"/>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" s="22"/>
       <c r="B156" s="22"/>
       <c r="C156" s="22"/>
@@ -15764,7 +15856,7 @@
       <c r="L156" s="20"/>
       <c r="M156" s="22"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" s="22"/>
       <c r="B157" s="22"/>
       <c r="C157" s="22"/>
@@ -15779,7 +15871,7 @@
       <c r="L157" s="20"/>
       <c r="M157" s="22"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" s="22"/>
       <c r="B158" s="22"/>
       <c r="C158" s="22"/>
@@ -15794,7 +15886,7 @@
       <c r="L158" s="20"/>
       <c r="M158" s="22"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" s="22"/>
       <c r="B159" s="22"/>
       <c r="C159" s="22"/>
@@ -15809,7 +15901,7 @@
       <c r="L159" s="20"/>
       <c r="M159" s="22"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" s="22"/>
       <c r="B160" s="22"/>
       <c r="C160" s="22"/>
@@ -15824,7 +15916,7 @@
       <c r="L160" s="20"/>
       <c r="M160" s="22"/>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" s="22"/>
       <c r="B161" s="22"/>
       <c r="C161" s="22"/>
@@ -15839,7 +15931,7 @@
       <c r="L161" s="20"/>
       <c r="M161" s="22"/>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" s="22"/>
       <c r="B162" s="22"/>
       <c r="C162" s="22"/>
@@ -15854,7 +15946,7 @@
       <c r="L162" s="20"/>
       <c r="M162" s="22"/>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" s="22"/>
       <c r="B163" s="22"/>
       <c r="C163" s="22"/>
@@ -15869,7 +15961,7 @@
       <c r="L163" s="20"/>
       <c r="M163" s="22"/>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" s="22"/>
       <c r="B164" s="22"/>
       <c r="C164" s="22"/>
@@ -15884,7 +15976,7 @@
       <c r="L164" s="20"/>
       <c r="M164" s="22"/>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" s="22"/>
       <c r="B165" s="22"/>
       <c r="C165" s="22"/>
@@ -15899,7 +15991,7 @@
       <c r="L165" s="20"/>
       <c r="M165" s="22"/>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A166" s="22"/>
       <c r="B166" s="22"/>
       <c r="C166" s="22"/>
@@ -15914,7 +16006,7 @@
       <c r="L166" s="20"/>
       <c r="M166" s="22"/>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A167" s="22"/>
       <c r="B167" s="22"/>
       <c r="C167" s="22"/>
@@ -15929,7 +16021,7 @@
       <c r="L167" s="20"/>
       <c r="M167" s="22"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A168" s="22"/>
       <c r="B168" s="22"/>
       <c r="C168" s="22"/>
@@ -15944,7 +16036,7 @@
       <c r="L168" s="20"/>
       <c r="M168" s="22"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A169" s="22"/>
       <c r="B169" s="22"/>
       <c r="C169" s="22"/>
@@ -15959,7 +16051,7 @@
       <c r="L169" s="20"/>
       <c r="M169" s="22"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A170" s="22"/>
       <c r="B170" s="22"/>
       <c r="C170" s="22"/>
@@ -15974,7 +16066,7 @@
       <c r="L170" s="20"/>
       <c r="M170" s="22"/>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A171" s="22"/>
       <c r="B171" s="22"/>
       <c r="C171" s="22"/>
@@ -15989,7 +16081,7 @@
       <c r="L171" s="20"/>
       <c r="M171" s="22"/>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A172" s="22"/>
       <c r="B172" s="22"/>
       <c r="C172" s="22"/>
@@ -16004,7 +16096,7 @@
       <c r="L172" s="20"/>
       <c r="M172" s="22"/>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A173" s="22"/>
       <c r="B173" s="22"/>
       <c r="C173" s="22"/>
@@ -16019,7 +16111,7 @@
       <c r="L173" s="20"/>
       <c r="M173" s="22"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A174" s="22"/>
       <c r="B174" s="22"/>
       <c r="C174" s="22"/>
@@ -16034,7 +16126,7 @@
       <c r="L174" s="20"/>
       <c r="M174" s="22"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A175" s="22"/>
       <c r="B175" s="22"/>
       <c r="C175" s="22"/>
@@ -16049,7 +16141,7 @@
       <c r="L175" s="20"/>
       <c r="M175" s="22"/>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A176" s="22"/>
       <c r="B176" s="22"/>
       <c r="C176" s="22"/>
@@ -16064,7 +16156,7 @@
       <c r="L176" s="20"/>
       <c r="M176" s="22"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A177" s="22"/>
       <c r="B177" s="22"/>
       <c r="C177" s="22"/>
@@ -16079,7 +16171,7 @@
       <c r="L177" s="20"/>
       <c r="M177" s="22"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A178" s="22"/>
       <c r="B178" s="22"/>
       <c r="C178" s="22"/>
@@ -16094,7 +16186,7 @@
       <c r="L178" s="20"/>
       <c r="M178" s="22"/>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A179" s="22"/>
       <c r="B179" s="22"/>
       <c r="C179" s="22"/>
@@ -16109,7 +16201,7 @@
       <c r="L179" s="20"/>
       <c r="M179" s="22"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A180" s="22"/>
       <c r="B180" s="22"/>
       <c r="C180" s="22"/>
@@ -16124,7 +16216,7 @@
       <c r="L180" s="20"/>
       <c r="M180" s="22"/>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A181" s="22"/>
       <c r="B181" s="22"/>
       <c r="C181" s="22"/>
@@ -16139,7 +16231,7 @@
       <c r="L181" s="20"/>
       <c r="M181" s="22"/>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A182" s="22"/>
       <c r="B182" s="22"/>
       <c r="C182" s="22"/>
@@ -16154,7 +16246,7 @@
       <c r="L182" s="20"/>
       <c r="M182" s="22"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A183" s="22"/>
       <c r="B183" s="22"/>
       <c r="C183" s="22"/>
@@ -16169,7 +16261,7 @@
       <c r="L183" s="20"/>
       <c r="M183" s="22"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A184" s="22"/>
       <c r="B184" s="22"/>
       <c r="C184" s="22"/>
@@ -16184,7 +16276,7 @@
       <c r="L184" s="20"/>
       <c r="M184" s="22"/>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A185" s="22"/>
       <c r="B185" s="22"/>
       <c r="C185" s="22"/>
@@ -16199,7 +16291,7 @@
       <c r="L185" s="20"/>
       <c r="M185" s="22"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A186" s="22"/>
       <c r="B186" s="22"/>
       <c r="C186" s="22"/>
@@ -16214,7 +16306,7 @@
       <c r="L186" s="20"/>
       <c r="M186" s="22"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A187" s="22"/>
       <c r="B187" s="22"/>
       <c r="C187" s="22"/>
@@ -16229,7 +16321,7 @@
       <c r="L187" s="20"/>
       <c r="M187" s="22"/>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A188" s="22"/>
       <c r="B188" s="22"/>
       <c r="C188" s="22"/>
@@ -16244,7 +16336,7 @@
       <c r="L188" s="20"/>
       <c r="M188" s="22"/>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A189" s="22"/>
       <c r="B189" s="22"/>
       <c r="C189" s="22"/>
@@ -16259,7 +16351,7 @@
       <c r="L189" s="20"/>
       <c r="M189" s="22"/>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A190" s="22"/>
       <c r="B190" s="22"/>
       <c r="C190" s="22"/>
@@ -16274,7 +16366,7 @@
       <c r="L190" s="20"/>
       <c r="M190" s="22"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A191" s="22"/>
       <c r="B191" s="22"/>
       <c r="C191" s="22"/>
@@ -16289,7 +16381,7 @@
       <c r="L191" s="20"/>
       <c r="M191" s="22"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A192" s="22"/>
       <c r="B192" s="22"/>
       <c r="C192" s="22"/>
@@ -16304,7 +16396,7 @@
       <c r="L192" s="20"/>
       <c r="M192" s="22"/>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A193" s="22"/>
       <c r="B193" s="22"/>
       <c r="C193" s="22"/>
@@ -16319,7 +16411,7 @@
       <c r="L193" s="20"/>
       <c r="M193" s="22"/>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A194" s="22"/>
       <c r="B194" s="22"/>
       <c r="C194" s="22"/>
@@ -16334,7 +16426,7 @@
       <c r="L194" s="20"/>
       <c r="M194" s="22"/>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A195" s="22"/>
       <c r="B195" s="22"/>
       <c r="C195" s="22"/>
@@ -16349,7 +16441,7 @@
       <c r="L195" s="20"/>
       <c r="M195" s="22"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A196" s="22"/>
       <c r="B196" s="22"/>
       <c r="C196" s="22"/>
@@ -16364,7 +16456,7 @@
       <c r="L196" s="20"/>
       <c r="M196" s="22"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A197" s="22"/>
       <c r="B197" s="22"/>
       <c r="C197" s="22"/>
@@ -16379,7 +16471,7 @@
       <c r="L197" s="20"/>
       <c r="M197" s="22"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A198" s="22"/>
       <c r="B198" s="22"/>
       <c r="C198" s="22"/>
@@ -16394,7 +16486,7 @@
       <c r="L198" s="20"/>
       <c r="M198" s="22"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A199" s="22"/>
       <c r="B199" s="22"/>
       <c r="C199" s="22"/>
@@ -16409,7 +16501,7 @@
       <c r="L199" s="20"/>
       <c r="M199" s="22"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A200" s="22"/>
       <c r="B200" s="22"/>
       <c r="C200" s="22"/>
@@ -16424,7 +16516,7 @@
       <c r="L200" s="20"/>
       <c r="M200" s="22"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A201" s="22"/>
       <c r="B201" s="22"/>
       <c r="C201" s="22"/>
@@ -16467,7 +16559,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -16481,7 +16573,7 @@
     <col min="15" max="15" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>153</v>
       </c>
@@ -16525,7 +16617,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="26" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>88</v>
       </c>
@@ -16573,7 +16665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -16595,7 +16687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="22"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -16617,7 +16709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="22"/>
       <c r="B5" s="22"/>
       <c r="C5" s="22"/>
@@ -16632,7 +16724,7 @@
       <c r="L5" s="22"/>
       <c r="M5" s="22"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="22"/>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
@@ -16647,7 +16739,7 @@
       <c r="L6" s="22"/>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="22"/>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -16662,7 +16754,7 @@
       <c r="L7" s="22"/>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="22"/>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -16677,7 +16769,7 @@
       <c r="L8" s="22"/>
       <c r="M8" s="22"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="22"/>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -16692,7 +16784,7 @@
       <c r="L9" s="22"/>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
@@ -16707,7 +16799,7 @@
       <c r="L10" s="22"/>
       <c r="M10" s="22"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="22"/>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -16722,7 +16814,7 @@
       <c r="L11" s="22"/>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="22"/>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -16737,7 +16829,7 @@
       <c r="L12" s="22"/>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="22"/>
       <c r="B13" s="22"/>
       <c r="C13" s="22"/>
@@ -16752,7 +16844,7 @@
       <c r="L13" s="22"/>
       <c r="M13" s="22"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="22"/>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -16767,7 +16859,7 @@
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="22"/>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -16782,7 +16874,7 @@
       <c r="L15" s="22"/>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -16797,7 +16889,7 @@
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="22"/>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -16812,7 +16904,7 @@
       <c r="L17" s="22"/>
       <c r="M17" s="22"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="22"/>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -16827,7 +16919,7 @@
       <c r="L18" s="22"/>
       <c r="M18" s="22"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="22"/>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -16842,7 +16934,7 @@
       <c r="L19" s="22"/>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -16857,7 +16949,7 @@
       <c r="L20" s="22"/>
       <c r="M20" s="22"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
@@ -16872,7 +16964,7 @@
       <c r="L21" s="22"/>
       <c r="M21" s="22"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="22"/>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -16887,7 +16979,7 @@
       <c r="L22" s="22"/>
       <c r="M22" s="22"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -16902,7 +16994,7 @@
       <c r="L23" s="22"/>
       <c r="M23" s="22"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -16917,7 +17009,7 @@
       <c r="L24" s="22"/>
       <c r="M24" s="22"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -16932,7 +17024,7 @@
       <c r="L25" s="22"/>
       <c r="M25" s="22"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -16947,7 +17039,7 @@
       <c r="L26" s="22"/>
       <c r="M26" s="22"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="22"/>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -16962,7 +17054,7 @@
       <c r="L27" s="22"/>
       <c r="M27" s="22"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -16977,7 +17069,7 @@
       <c r="L28" s="22"/>
       <c r="M28" s="22"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -16992,7 +17084,7 @@
       <c r="L29" s="22"/>
       <c r="M29" s="22"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="22"/>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
@@ -17007,7 +17099,7 @@
       <c r="L30" s="22"/>
       <c r="M30" s="22"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -17022,7 +17114,7 @@
       <c r="L31" s="22"/>
       <c r="M31" s="22"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
@@ -17037,7 +17129,7 @@
       <c r="L32" s="22"/>
       <c r="M32" s="22"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="22"/>
@@ -17052,7 +17144,7 @@
       <c r="L33" s="22"/>
       <c r="M33" s="22"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
@@ -17067,7 +17159,7 @@
       <c r="L34" s="22"/>
       <c r="M34" s="22"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="22"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
@@ -17082,7 +17174,7 @@
       <c r="L35" s="22"/>
       <c r="M35" s="22"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="22"/>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
@@ -17097,7 +17189,7 @@
       <c r="L36" s="22"/>
       <c r="M36" s="22"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="22"/>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
@@ -17112,7 +17204,7 @@
       <c r="L37" s="22"/>
       <c r="M37" s="22"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="22"/>
       <c r="B38" s="22"/>
       <c r="C38" s="22"/>
@@ -17127,7 +17219,7 @@
       <c r="L38" s="22"/>
       <c r="M38" s="22"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="22"/>
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
@@ -17142,7 +17234,7 @@
       <c r="L39" s="22"/>
       <c r="M39" s="22"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="22"/>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -17157,7 +17249,7 @@
       <c r="L40" s="22"/>
       <c r="M40" s="22"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="22"/>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -17172,7 +17264,7 @@
       <c r="L41" s="22"/>
       <c r="M41" s="22"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="22"/>
       <c r="B42" s="22"/>
       <c r="C42" s="22"/>
@@ -17187,7 +17279,7 @@
       <c r="L42" s="22"/>
       <c r="M42" s="22"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="22"/>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
@@ -17202,7 +17294,7 @@
       <c r="L43" s="22"/>
       <c r="M43" s="22"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="22"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -17217,7 +17309,7 @@
       <c r="L44" s="22"/>
       <c r="M44" s="22"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="22"/>
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
@@ -17232,7 +17324,7 @@
       <c r="L45" s="22"/>
       <c r="M45" s="22"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="22"/>
       <c r="B46" s="22"/>
       <c r="C46" s="22"/>
@@ -17247,7 +17339,7 @@
       <c r="L46" s="22"/>
       <c r="M46" s="22"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="22"/>
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
@@ -17262,7 +17354,7 @@
       <c r="L47" s="22"/>
       <c r="M47" s="22"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="22"/>
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
@@ -17277,7 +17369,7 @@
       <c r="L48" s="22"/>
       <c r="M48" s="22"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="22"/>
       <c r="B49" s="22"/>
       <c r="C49" s="22"/>
@@ -17292,7 +17384,7 @@
       <c r="L49" s="22"/>
       <c r="M49" s="22"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="22"/>
       <c r="B50" s="22"/>
       <c r="C50" s="22"/>
@@ -17307,7 +17399,7 @@
       <c r="L50" s="22"/>
       <c r="M50" s="22"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="22"/>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
@@ -17322,7 +17414,7 @@
       <c r="L51" s="22"/>
       <c r="M51" s="22"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="22"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -17337,7 +17429,7 @@
       <c r="L52" s="22"/>
       <c r="M52" s="22"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="22"/>
       <c r="B53" s="22"/>
       <c r="C53" s="22"/>
@@ -17352,7 +17444,7 @@
       <c r="L53" s="22"/>
       <c r="M53" s="22"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="22"/>
       <c r="B54" s="22"/>
       <c r="C54" s="22"/>
@@ -17367,7 +17459,7 @@
       <c r="L54" s="22"/>
       <c r="M54" s="22"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="22"/>
       <c r="B55" s="22"/>
       <c r="C55" s="22"/>
@@ -17382,7 +17474,7 @@
       <c r="L55" s="22"/>
       <c r="M55" s="22"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="22"/>
       <c r="B56" s="22"/>
       <c r="C56" s="22"/>
@@ -17397,7 +17489,7 @@
       <c r="L56" s="22"/>
       <c r="M56" s="22"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="22"/>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
@@ -17412,7 +17504,7 @@
       <c r="L57" s="22"/>
       <c r="M57" s="22"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="22"/>
       <c r="B58" s="22"/>
       <c r="C58" s="22"/>
@@ -17427,7 +17519,7 @@
       <c r="L58" s="22"/>
       <c r="M58" s="22"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="22"/>
       <c r="B59" s="22"/>
       <c r="C59" s="22"/>
@@ -17442,7 +17534,7 @@
       <c r="L59" s="22"/>
       <c r="M59" s="22"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="22"/>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -17457,7 +17549,7 @@
       <c r="L60" s="22"/>
       <c r="M60" s="22"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="22"/>
       <c r="B61" s="22"/>
       <c r="C61" s="22"/>
@@ -17472,7 +17564,7 @@
       <c r="L61" s="22"/>
       <c r="M61" s="22"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="22"/>
       <c r="B62" s="22"/>
       <c r="C62" s="22"/>
@@ -17487,7 +17579,7 @@
       <c r="L62" s="22"/>
       <c r="M62" s="22"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="22"/>
       <c r="B63" s="22"/>
       <c r="C63" s="22"/>
@@ -17502,7 +17594,7 @@
       <c r="L63" s="22"/>
       <c r="M63" s="22"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="22"/>
       <c r="B64" s="22"/>
       <c r="C64" s="22"/>
@@ -17517,7 +17609,7 @@
       <c r="L64" s="22"/>
       <c r="M64" s="22"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="22"/>
       <c r="B65" s="22"/>
       <c r="C65" s="22"/>
@@ -17532,7 +17624,7 @@
       <c r="L65" s="22"/>
       <c r="M65" s="22"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="22"/>
       <c r="B66" s="22"/>
       <c r="C66" s="22"/>
@@ -17547,7 +17639,7 @@
       <c r="L66" s="22"/>
       <c r="M66" s="22"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="22"/>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -17562,7 +17654,7 @@
       <c r="L67" s="22"/>
       <c r="M67" s="22"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="22"/>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -17577,7 +17669,7 @@
       <c r="L68" s="22"/>
       <c r="M68" s="22"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="22"/>
       <c r="B69" s="22"/>
       <c r="C69" s="22"/>
@@ -17592,7 +17684,7 @@
       <c r="L69" s="22"/>
       <c r="M69" s="22"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" s="22"/>
       <c r="B70" s="22"/>
       <c r="C70" s="22"/>
@@ -17607,7 +17699,7 @@
       <c r="L70" s="22"/>
       <c r="M70" s="22"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" s="22"/>
       <c r="B71" s="22"/>
       <c r="C71" s="22"/>
@@ -17622,7 +17714,7 @@
       <c r="L71" s="22"/>
       <c r="M71" s="22"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" s="22"/>
       <c r="B72" s="22"/>
       <c r="C72" s="22"/>
@@ -17637,7 +17729,7 @@
       <c r="L72" s="22"/>
       <c r="M72" s="22"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" s="22"/>
       <c r="B73" s="22"/>
       <c r="C73" s="22"/>
@@ -17652,7 +17744,7 @@
       <c r="L73" s="22"/>
       <c r="M73" s="22"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" s="22"/>
       <c r="B74" s="22"/>
       <c r="C74" s="22"/>
@@ -17667,7 +17759,7 @@
       <c r="L74" s="22"/>
       <c r="M74" s="22"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" s="22"/>
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
@@ -17682,7 +17774,7 @@
       <c r="L75" s="22"/>
       <c r="M75" s="22"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" s="22"/>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -17697,7 +17789,7 @@
       <c r="L76" s="22"/>
       <c r="M76" s="22"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" s="22"/>
       <c r="B77" s="22"/>
       <c r="C77" s="22"/>
@@ -17712,7 +17804,7 @@
       <c r="L77" s="22"/>
       <c r="M77" s="22"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" s="22"/>
       <c r="B78" s="22"/>
       <c r="C78" s="22"/>
@@ -17727,7 +17819,7 @@
       <c r="L78" s="22"/>
       <c r="M78" s="22"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" s="22"/>
       <c r="B79" s="22"/>
       <c r="C79" s="22"/>
@@ -17742,7 +17834,7 @@
       <c r="L79" s="22"/>
       <c r="M79" s="22"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" s="22"/>
       <c r="B80" s="22"/>
       <c r="C80" s="22"/>
@@ -17757,7 +17849,7 @@
       <c r="L80" s="22"/>
       <c r="M80" s="22"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="22"/>
       <c r="B81" s="22"/>
       <c r="C81" s="22"/>
@@ -17772,7 +17864,7 @@
       <c r="L81" s="22"/>
       <c r="M81" s="22"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="22"/>
       <c r="B82" s="22"/>
       <c r="C82" s="22"/>
@@ -17787,7 +17879,7 @@
       <c r="L82" s="22"/>
       <c r="M82" s="22"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="22"/>
       <c r="B83" s="22"/>
       <c r="C83" s="22"/>
@@ -17802,7 +17894,7 @@
       <c r="L83" s="22"/>
       <c r="M83" s="22"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="22"/>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -17817,7 +17909,7 @@
       <c r="L84" s="22"/>
       <c r="M84" s="22"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="22"/>
       <c r="B85" s="22"/>
       <c r="C85" s="22"/>
@@ -17832,7 +17924,7 @@
       <c r="L85" s="22"/>
       <c r="M85" s="22"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="22"/>
       <c r="B86" s="22"/>
       <c r="C86" s="22"/>
@@ -17847,7 +17939,7 @@
       <c r="L86" s="22"/>
       <c r="M86" s="22"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" s="22"/>
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
@@ -17862,7 +17954,7 @@
       <c r="L87" s="22"/>
       <c r="M87" s="22"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" s="22"/>
       <c r="B88" s="22"/>
       <c r="C88" s="22"/>
@@ -17877,7 +17969,7 @@
       <c r="L88" s="22"/>
       <c r="M88" s="22"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" s="22"/>
       <c r="B89" s="22"/>
       <c r="C89" s="22"/>
@@ -17892,7 +17984,7 @@
       <c r="L89" s="22"/>
       <c r="M89" s="22"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" s="22"/>
       <c r="B90" s="22"/>
       <c r="C90" s="22"/>
@@ -17907,7 +17999,7 @@
       <c r="L90" s="22"/>
       <c r="M90" s="22"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="22"/>
       <c r="B91" s="22"/>
       <c r="C91" s="22"/>
@@ -17922,7 +18014,7 @@
       <c r="L91" s="22"/>
       <c r="M91" s="22"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="22"/>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -17937,7 +18029,7 @@
       <c r="L92" s="22"/>
       <c r="M92" s="22"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" s="22"/>
       <c r="B93" s="22"/>
       <c r="C93" s="22"/>
@@ -17952,7 +18044,7 @@
       <c r="L93" s="22"/>
       <c r="M93" s="22"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" s="22"/>
       <c r="B94" s="22"/>
       <c r="C94" s="22"/>
@@ -17967,7 +18059,7 @@
       <c r="L94" s="22"/>
       <c r="M94" s="22"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" s="22"/>
       <c r="B95" s="22"/>
       <c r="C95" s="22"/>
@@ -17982,7 +18074,7 @@
       <c r="L95" s="22"/>
       <c r="M95" s="22"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" s="22"/>
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
@@ -17997,7 +18089,7 @@
       <c r="L96" s="22"/>
       <c r="M96" s="22"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="22"/>
       <c r="B97" s="22"/>
       <c r="C97" s="22"/>
@@ -18012,7 +18104,7 @@
       <c r="L97" s="22"/>
       <c r="M97" s="22"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="22"/>
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
@@ -18027,7 +18119,7 @@
       <c r="L98" s="22"/>
       <c r="M98" s="22"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="22"/>
       <c r="B99" s="22"/>
       <c r="C99" s="22"/>
@@ -18042,7 +18134,7 @@
       <c r="L99" s="22"/>
       <c r="M99" s="22"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" s="22"/>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -18057,7 +18149,7 @@
       <c r="L100" s="22"/>
       <c r="M100" s="22"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" s="22"/>
       <c r="B101" s="22"/>
       <c r="C101" s="22"/>
